--- a/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-31</t>
+    <t>2024-11-18</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3828" uniqueCount="563">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3828" uniqueCount="562">
   <si>
     <t>Property</t>
   </si>
@@ -930,6 +930,9 @@
     <t>このObservationに関するLOINC上の分類、必須項目</t>
   </si>
   <si>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationDentalCategory_VS</t>
+  </si>
+  <si>
     <t>Observation.category:second.id</t>
   </si>
   <si>
@@ -963,9 +966,6 @@
     <t>Observation.category:second.coding.display</t>
   </si>
   <si>
-    <t>Dental</t>
-  </si>
-  <si>
     <t>Observation.category:second.coding.userSelected</t>
   </si>
   <si>
@@ -978,10 +978,10 @@
     <t>third</t>
   </si>
   <si>
-    <t>このObservationに関する詳細分類、JP_ObservationDentalCategory_VSより選択する、必須項目</t>
-  </si>
-  <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationDentalCategory_VS</t>
+    <t>このObservationに関する詳細分類、JP_ObservationDetailedDentalCategory_VSより選択する、必須項目</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationDetailedDentalCategory_VS</t>
   </si>
   <si>
     <t>Observation.category:third.id</t>
@@ -1015,9 +1015,6 @@
   </si>
   <si>
     <t>Observation.category:third.coding.display</t>
-  </si>
-  <si>
-    <t>ToothExistence</t>
   </si>
   <si>
     <t>Observation.category:third.coding.userSelected</t>
@@ -2104,7 +2101,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="105.8828125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="63.09375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="70.58203125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -5561,11 +5558,11 @@
         <v>83</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>118</v>
+        <v>188</v>
       </c>
       <c r="Y29" s="2"/>
       <c r="Z29" t="s" s="2">
-        <v>202</v>
+        <v>294</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>83</v>
@@ -5618,7 +5615,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>211</v>
@@ -5736,7 +5733,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>218</v>
@@ -5856,7 +5853,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>224</v>
@@ -5978,7 +5975,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>234</v>
@@ -6096,7 +6093,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>236</v>
@@ -6216,7 +6213,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>238</v>
@@ -6261,7 +6258,7 @@
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>83</v>
@@ -6338,7 +6335,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>248</v>
@@ -6458,7 +6455,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>256</v>
@@ -6501,7 +6498,7 @@
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>83</v>
@@ -6578,7 +6575,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>265</v>
@@ -6624,7 +6621,7 @@
         <v>83</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>305</v>
+        <v>83</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>83</v>
@@ -8070,7 +8067,7 @@
         <v>83</v>
       </c>
       <c r="S50" t="s" s="2">
-        <v>323</v>
+        <v>83</v>
       </c>
       <c r="T50" t="s" s="2">
         <v>83</v>
@@ -8144,7 +8141,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>273</v>
@@ -8266,7 +8263,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B52" t="s" s="2">
         <v>283</v>
@@ -8388,14 +8385,14 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8417,16 +8414,16 @@
         <v>198</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="N53" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="M53" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="N53" t="s" s="2">
+      <c r="O53" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>330</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>83</v>
@@ -8451,14 +8448,14 @@
         <v>83</v>
       </c>
       <c r="X53" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="Y53" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="Y53" t="s" s="2">
+      <c r="Z53" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="Z53" t="s" s="2">
-        <v>333</v>
-      </c>
       <c r="AA53" t="s" s="2">
         <v>83</v>
       </c>
@@ -8475,7 +8472,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>94</v>
@@ -8490,30 +8487,30 @@
         <v>106</v>
       </c>
       <c r="AK53" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="AL53" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="AL53" t="s" s="2">
+      <c r="AM53" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="AM53" t="s" s="2">
+      <c r="AN53" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="AN53" t="s" s="2">
+      <c r="AO53" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="AO53" t="s" s="2">
+      <c r="AP53" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="AP53" t="s" s="2">
-        <v>339</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8628,10 +8625,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8748,10 +8745,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8777,10 +8774,10 @@
         <v>225</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="N56" t="s" s="2">
         <v>228</v>
@@ -8870,10 +8867,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8988,10 +8985,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9108,10 +9105,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9153,7 +9150,7 @@
       </c>
       <c r="Q59" s="2"/>
       <c r="R59" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="S59" t="s" s="2">
         <v>83</v>
@@ -9230,10 +9227,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9350,10 +9347,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9393,7 +9390,7 @@
       </c>
       <c r="Q61" s="2"/>
       <c r="R61" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="S61" t="s" s="2">
         <v>83</v>
@@ -9470,10 +9467,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9516,7 +9513,7 @@
         <v>83</v>
       </c>
       <c r="S62" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="T62" t="s" s="2">
         <v>83</v>
@@ -9590,10 +9587,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9712,10 +9709,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9834,10 +9831,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9860,19 +9857,19 @@
         <v>95</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="L65" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="L65" t="s" s="2">
+      <c r="M65" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="N65" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="M65" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="N65" t="s" s="2">
+      <c r="O65" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>83</v>
@@ -9921,7 +9918,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -9936,19 +9933,19 @@
         <v>106</v>
       </c>
       <c r="AK65" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM65" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="AL65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM65" t="s" s="2">
+      <c r="AN65" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="AN65" t="s" s="2">
+      <c r="AO65" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="AO65" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>83</v>
@@ -9956,10 +9953,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9982,7 +9979,7 @@
         <v>95</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="L66" t="s" s="2">
         <v>179</v>
@@ -9991,7 +9988,7 @@
         <v>179</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10041,7 +10038,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10062,13 +10059,13 @@
         <v>83</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>83</v>
@@ -10076,14 +10073,14 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10102,19 +10099,19 @@
         <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="L67" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="L67" t="s" s="2">
+      <c r="M67" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="N67" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="M67" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="N67" t="s" s="2">
+      <c r="O67" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
@@ -10163,7 +10160,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10178,19 +10175,19 @@
         <v>106</v>
       </c>
       <c r="AK67" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM67" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="AL67" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM67" t="s" s="2">
+      <c r="AN67" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="AN67" t="s" s="2">
+      <c r="AO67" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="AO67" t="s" s="2">
-        <v>376</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>83</v>
@@ -10198,14 +10195,14 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -10224,19 +10221,19 @@
         <v>95</v>
       </c>
       <c r="K68" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="L68" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="L68" t="s" s="2">
+      <c r="M68" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="N68" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="M68" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="N68" t="s" s="2">
+      <c r="O68" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>382</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>83</v>
@@ -10285,7 +10282,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10300,19 +10297,19 @@
         <v>106</v>
       </c>
       <c r="AK68" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM68" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="AL68" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM68" t="s" s="2">
+      <c r="AN68" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="AN68" t="s" s="2">
+      <c r="AO68" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="AO68" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>83</v>
@@ -10320,10 +10317,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10346,16 +10343,16 @@
         <v>95</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="L69" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="L69" t="s" s="2">
+      <c r="M69" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="N69" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>390</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10405,7 +10402,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10426,13 +10423,13 @@
         <v>83</v>
       </c>
       <c r="AM69" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AN69" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="AN69" t="s" s="2">
+      <c r="AO69" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="AO69" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>83</v>
@@ -10440,10 +10437,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10466,19 +10463,19 @@
         <v>95</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="L70" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="L70" t="s" s="2">
+      <c r="M70" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="N70" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="M70" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="N70" t="s" s="2">
+      <c r="O70" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>398</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>83</v>
@@ -10527,7 +10524,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10542,19 +10539,19 @@
         <v>106</v>
       </c>
       <c r="AK70" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM70" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="AL70" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM70" t="s" s="2">
+      <c r="AN70" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="AN70" t="s" s="2">
+      <c r="AO70" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="AO70" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>83</v>
@@ -10562,10 +10559,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10591,16 +10588,16 @@
         <v>198</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="N71" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="M71" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="N71" t="s" s="2">
+      <c r="O71" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>83</v>
@@ -10629,7 +10626,7 @@
       </c>
       <c r="Y71" s="2"/>
       <c r="Z71" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>83</v>
@@ -10647,7 +10644,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10656,7 +10653,7 @@
         <v>94</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>106</v>
@@ -10665,27 +10662,27 @@
         <v>83</v>
       </c>
       <c r="AL71" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AM71" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="AM71" t="s" s="2">
+      <c r="AN71" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="AN71" t="s" s="2">
+      <c r="AO71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP71" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="AO71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP71" t="s" s="2">
-        <v>412</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10711,16 +10708,16 @@
         <v>198</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="N72" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="M72" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="N72" t="s" s="2">
+      <c r="O72" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>83</v>
@@ -10745,14 +10742,14 @@
         <v>83</v>
       </c>
       <c r="X72" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="Y72" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="Y72" t="s" s="2">
+      <c r="Z72" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="Z72" t="s" s="2">
-        <v>419</v>
-      </c>
       <c r="AA72" t="s" s="2">
         <v>83</v>
       </c>
@@ -10769,7 +10766,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -10778,7 +10775,7 @@
         <v>94</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>106</v>
@@ -10793,7 +10790,7 @@
         <v>137</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>83</v>
@@ -10804,14 +10801,14 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -10839,10 +10836,10 @@
         <v>179</v>
       </c>
       <c r="N73" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="O73" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>425</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>83</v>
@@ -10867,14 +10864,14 @@
         <v>83</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="Y73" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="Z73" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="Z73" t="s" s="2">
-        <v>427</v>
-      </c>
       <c r="AA73" t="s" s="2">
         <v>83</v>
       </c>
@@ -10891,7 +10888,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -10909,27 +10906,27 @@
         <v>83</v>
       </c>
       <c r="AL73" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AM73" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="AM73" t="s" s="2">
+      <c r="AN73" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="AN73" t="s" s="2">
+      <c r="AO73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP73" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="AO73" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP73" t="s" s="2">
-        <v>431</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10952,7 +10949,7 @@
         <v>83</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="L74" t="s" s="2">
         <v>179</v>
@@ -10961,10 +10958,10 @@
         <v>179</v>
       </c>
       <c r="N74" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="O74" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>83</v>
@@ -11013,7 +11010,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11034,10 +11031,10 @@
         <v>83</v>
       </c>
       <c r="AM74" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="AN74" t="s" s="2">
         <v>436</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>437</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>83</v>
@@ -11048,10 +11045,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11077,13 +11074,13 @@
         <v>198</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="N75" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>440</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11113,7 +11110,7 @@
       </c>
       <c r="Y75" s="2"/>
       <c r="Z75" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>83</v>
@@ -11131,7 +11128,7 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11149,27 +11146,27 @@
         <v>83</v>
       </c>
       <c r="AL75" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AM75" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="AM75" t="s" s="2">
+      <c r="AN75" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="AN75" t="s" s="2">
+      <c r="AO75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP75" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="AO75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP75" t="s" s="2">
-        <v>445</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11195,16 +11192,16 @@
         <v>198</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="N76" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="M76" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="N76" t="s" s="2">
+      <c r="O76" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>449</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>83</v>
@@ -11229,14 +11226,14 @@
         <v>83</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="Y76" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="Z76" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="Z76" t="s" s="2">
-        <v>451</v>
-      </c>
       <c r="AA76" t="s" s="2">
         <v>83</v>
       </c>
@@ -11253,7 +11250,7 @@
         <v>83</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11274,10 +11271,10 @@
         <v>83</v>
       </c>
       <c r="AM76" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AN76" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>83</v>
@@ -11288,10 +11285,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11314,7 +11311,7 @@
         <v>83</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="L77" t="s" s="2">
         <v>179</v>
@@ -11323,7 +11320,7 @@
         <v>179</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11373,7 +11370,7 @@
         <v>83</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11391,27 +11388,27 @@
         <v>83</v>
       </c>
       <c r="AL77" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="AM77" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="AM77" t="s" s="2">
+      <c r="AN77" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="AN77" t="s" s="2">
+      <c r="AO77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP77" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="AO77" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP77" t="s" s="2">
-        <v>460</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11434,16 +11431,16 @@
         <v>83</v>
       </c>
       <c r="K78" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="L78" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="L78" t="s" s="2">
+      <c r="M78" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="N78" t="s" s="2">
         <v>463</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11493,7 +11490,7 @@
         <v>83</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11511,27 +11508,27 @@
         <v>83</v>
       </c>
       <c r="AL78" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="AM78" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="AM78" t="s" s="2">
+      <c r="AN78" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="AN78" t="s" s="2">
+      <c r="AO78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP78" t="s" s="2">
         <v>467</v>
-      </c>
-      <c r="AO78" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP78" t="s" s="2">
-        <v>468</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11554,7 +11551,7 @@
         <v>83</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="L79" t="s" s="2">
         <v>179</v>
@@ -11563,10 +11560,10 @@
         <v>179</v>
       </c>
       <c r="N79" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="O79" t="s" s="2">
         <v>471</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>472</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>83</v>
@@ -11615,7 +11612,7 @@
         <v>83</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -11627,19 +11624,19 @@
         <v>83</v>
       </c>
       <c r="AJ79" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM79" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="AK79" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL79" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM79" t="s" s="2">
+      <c r="AN79" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="AN79" t="s" s="2">
-        <v>475</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>83</v>
@@ -11650,10 +11647,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11768,10 +11765,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11888,14 +11885,14 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -11917,10 +11914,10 @@
         <v>139</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="M82" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>481</v>
       </c>
       <c r="N82" t="s" s="2">
         <v>156</v>
@@ -11975,7 +11972,7 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -12010,10 +12007,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12036,13 +12033,13 @@
         <v>83</v>
       </c>
       <c r="K83" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="L83" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="L83" t="s" s="2">
+      <c r="M83" t="s" s="2">
         <v>485</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>486</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -12093,7 +12090,7 @@
         <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12102,7 +12099,7 @@
         <v>94</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>106</v>
@@ -12114,10 +12111,10 @@
         <v>83</v>
       </c>
       <c r="AM83" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AN83" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="AN83" t="s" s="2">
-        <v>489</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>83</v>
@@ -12128,10 +12125,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12154,13 +12151,13 @@
         <v>83</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>492</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -12211,7 +12208,7 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12220,7 +12217,7 @@
         <v>94</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="AJ84" t="s" s="2">
         <v>106</v>
@@ -12232,10 +12229,10 @@
         <v>83</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>83</v>
@@ -12246,10 +12243,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12275,16 +12272,16 @@
         <v>198</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>495</v>
       </c>
-      <c r="M85" t="s" s="2">
+      <c r="N85" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="N85" t="s" s="2">
+      <c r="O85" t="s" s="2">
         <v>497</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>83</v>
@@ -12312,11 +12309,11 @@
         <v>118</v>
       </c>
       <c r="Y85" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="Z85" t="s" s="2">
         <v>499</v>
       </c>
-      <c r="Z85" t="s" s="2">
-        <v>500</v>
-      </c>
       <c r="AA85" t="s" s="2">
         <v>83</v>
       </c>
@@ -12333,7 +12330,7 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12351,13 +12348,13 @@
         <v>83</v>
       </c>
       <c r="AL85" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="AM85" t="s" s="2">
         <v>501</v>
       </c>
-      <c r="AM85" t="s" s="2">
-        <v>502</v>
-      </c>
       <c r="AN85" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>83</v>
@@ -12368,10 +12365,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12397,16 +12394,16 @@
         <v>198</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>504</v>
       </c>
-      <c r="M86" t="s" s="2">
+      <c r="N86" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="N86" t="s" s="2">
+      <c r="O86" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>507</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>83</v>
@@ -12431,14 +12428,14 @@
         <v>83</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="Y86" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="Z86" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="Z86" t="s" s="2">
-        <v>509</v>
-      </c>
       <c r="AA86" t="s" s="2">
         <v>83</v>
       </c>
@@ -12455,7 +12452,7 @@
         <v>83</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -12473,13 +12470,13 @@
         <v>83</v>
       </c>
       <c r="AL86" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="AM86" t="s" s="2">
         <v>501</v>
       </c>
-      <c r="AM86" t="s" s="2">
-        <v>502</v>
-      </c>
       <c r="AN86" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>83</v>
@@ -12490,10 +12487,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12516,17 +12513,17 @@
         <v>83</v>
       </c>
       <c r="K87" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="L87" t="s" s="2">
         <v>511</v>
       </c>
-      <c r="L87" t="s" s="2">
+      <c r="M87" t="s" s="2">
         <v>512</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>513</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>83</v>
@@ -12575,7 +12572,7 @@
         <v>83</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -12599,7 +12596,7 @@
         <v>83</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>83</v>
@@ -12610,10 +12607,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12639,10 +12636,10 @@
         <v>212</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>517</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>518</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12693,7 +12690,7 @@
         <v>83</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -12714,10 +12711,10 @@
         <v>83</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>83</v>
@@ -12728,10 +12725,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12754,16 +12751,16 @@
         <v>95</v>
       </c>
       <c r="K89" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="L89" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="L89" t="s" s="2">
+      <c r="M89" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="N89" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>523</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -12813,7 +12810,7 @@
         <v>83</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -12834,10 +12831,10 @@
         <v>83</v>
       </c>
       <c r="AM89" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="AN89" t="s" s="2">
         <v>524</v>
-      </c>
-      <c r="AN89" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>83</v>
@@ -12848,10 +12845,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12874,7 +12871,7 @@
         <v>95</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="L90" t="s" s="2">
         <v>179</v>
@@ -12883,7 +12880,7 @@
         <v>179</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -12933,7 +12930,7 @@
         <v>83</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -12954,10 +12951,10 @@
         <v>83</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>83</v>
@@ -12968,10 +12965,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12994,7 +12991,7 @@
         <v>95</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="L91" t="s" s="2">
         <v>179</v>
@@ -13003,10 +13000,10 @@
         <v>179</v>
       </c>
       <c r="N91" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="O91" t="s" s="2">
         <v>531</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>532</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>83</v>
@@ -13055,7 +13052,7 @@
         <v>83</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -13076,10 +13073,10 @@
         <v>83</v>
       </c>
       <c r="AM91" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="AN91" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="AN91" t="s" s="2">
-        <v>534</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>83</v>
@@ -13090,10 +13087,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13208,10 +13205,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13328,14 +13325,14 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
@@ -13357,10 +13354,10 @@
         <v>139</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>481</v>
       </c>
       <c r="N94" t="s" s="2">
         <v>156</v>
@@ -13415,7 +13412,7 @@
         <v>83</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -13450,10 +13447,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13479,16 +13476,16 @@
         <v>198</v>
       </c>
       <c r="L95" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="M95" t="s" s="2">
         <v>539</v>
       </c>
-      <c r="M95" t="s" s="2">
+      <c r="N95" t="s" s="2">
         <v>540</v>
       </c>
-      <c r="N95" t="s" s="2">
-        <v>541</v>
-      </c>
       <c r="O95" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>83</v>
@@ -13513,14 +13510,14 @@
         <v>83</v>
       </c>
       <c r="X95" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="Y95" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="Y95" t="s" s="2">
+      <c r="Z95" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="Z95" t="s" s="2">
-        <v>333</v>
-      </c>
       <c r="AA95" t="s" s="2">
         <v>83</v>
       </c>
@@ -13537,7 +13534,7 @@
         <v>83</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>94</v>
@@ -13555,16 +13552,16 @@
         <v>83</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="AM95" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AN95" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="AN95" t="s" s="2">
+      <c r="AO95" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="AO95" t="s" s="2">
-        <v>338</v>
       </c>
       <c r="AP95" t="s" s="2">
         <v>83</v>
@@ -13572,10 +13569,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13598,19 +13595,19 @@
         <v>95</v>
       </c>
       <c r="K96" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="L96" t="s" s="2">
         <v>544</v>
       </c>
-      <c r="L96" t="s" s="2">
+      <c r="M96" t="s" s="2">
         <v>545</v>
       </c>
-      <c r="M96" t="s" s="2">
+      <c r="N96" t="s" s="2">
         <v>546</v>
       </c>
-      <c r="N96" t="s" s="2">
-        <v>547</v>
-      </c>
       <c r="O96" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>83</v>
@@ -13659,7 +13656,7 @@
         <v>83</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
@@ -13677,27 +13674,27 @@
         <v>83</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="AM96" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AN96" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="AN96" t="s" s="2">
+      <c r="AO96" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP96" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="AO96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP96" t="s" s="2">
-        <v>412</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13723,16 +13720,16 @@
         <v>198</v>
       </c>
       <c r="L97" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="M97" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="M97" t="s" s="2">
+      <c r="N97" t="s" s="2">
         <v>551</v>
       </c>
-      <c r="N97" t="s" s="2">
-        <v>552</v>
-      </c>
       <c r="O97" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>83</v>
@@ -13757,14 +13754,14 @@
         <v>83</v>
       </c>
       <c r="X97" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="Y97" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="Y97" t="s" s="2">
+      <c r="Z97" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="Z97" t="s" s="2">
-        <v>419</v>
-      </c>
       <c r="AA97" t="s" s="2">
         <v>83</v>
       </c>
@@ -13781,7 +13778,7 @@
         <v>83</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
@@ -13790,7 +13787,7 @@
         <v>94</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AJ97" t="s" s="2">
         <v>106</v>
@@ -13805,7 +13802,7 @@
         <v>137</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>83</v>
@@ -13816,14 +13813,14 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
@@ -13845,16 +13842,16 @@
         <v>198</v>
       </c>
       <c r="L98" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="M98" t="s" s="2">
         <v>554</v>
       </c>
-      <c r="M98" t="s" s="2">
+      <c r="N98" t="s" s="2">
         <v>555</v>
       </c>
-      <c r="N98" t="s" s="2">
+      <c r="O98" t="s" s="2">
         <v>556</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>557</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>83</v>
@@ -13879,14 +13876,14 @@
         <v>83</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="Y98" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="Z98" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="Z98" t="s" s="2">
-        <v>427</v>
-      </c>
       <c r="AA98" t="s" s="2">
         <v>83</v>
       </c>
@@ -13903,7 +13900,7 @@
         <v>83</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -13921,27 +13918,27 @@
         <v>83</v>
       </c>
       <c r="AL98" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AM98" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="AM98" t="s" s="2">
+      <c r="AN98" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="AN98" t="s" s="2">
+      <c r="AO98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP98" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="AO98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP98" t="s" s="2">
-        <v>431</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13967,16 +13964,16 @@
         <v>84</v>
       </c>
       <c r="L99" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="M99" t="s" s="2">
         <v>559</v>
       </c>
-      <c r="M99" t="s" s="2">
+      <c r="N99" t="s" s="2">
         <v>560</v>
       </c>
-      <c r="N99" t="s" s="2">
+      <c r="O99" t="s" s="2">
         <v>561</v>
-      </c>
-      <c r="O99" t="s" s="2">
-        <v>562</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>83</v>
@@ -14025,7 +14022,7 @@
         <v>83</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>81</v>
@@ -14046,10 +14043,10 @@
         <v>83</v>
       </c>
       <c r="AM99" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="AN99" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="AN99" t="s" s="2">
-        <v>475</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>83</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
@@ -282,7 +282,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidまたはmeta.lastupdatedを持たないものとします / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}obs-6:databsentrasonは、観察.value [x]が存在しない場合にのみ存在するものとします / dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:visserveration.codeがvisserveration.component.codeと同じ場合、コードに関連付けられている値要素が存在しないでください / If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}obs-6:databsentrasonは、観察.value [x]が存在しない場合にのみ存在するものとします / dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:visserveration.codeがvisserveration.component.codeと同じ場合、コードに関連付けられている値要素が存在しないでください / If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -329,16 +329,16 @@
 </t>
   </si>
   <si>
-    <t>リソースに関するメタデータ / Metadata about the resource</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -464,7 +464,7 @@
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -1483,7 +1483,7 @@
     <t>どの値が「正常」と見なされるかを知ることは、特定の結果の意義を評価するのに役立つ。さまざまなコンテキストに対応するため複数の参照範囲を提供できる必要がある。</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 obs-3:少なくとも低いまたは高またはテキストが必要です / Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
   </si>
   <si>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3828" uniqueCount="562">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3830" uniqueCount="564">
   <si>
     <t>Property</t>
   </si>
@@ -650,7 +650,10 @@
     <t>どの観測値が取得されて表示されるかをフィルタリングするために使用されます。 / Used for filtering what observations are retrieved and displayed.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS</t>
+    <t>高レベルの観測カテゴリのコード。 / Codes for high level observation categories.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
   </si>
   <si>
     <t xml:space="preserve">value:coding.system}
@@ -672,7 +675,10 @@
     <t>このObservationに関する分類（JP_SimpleObservationCategory_VS）、必須項目</t>
   </si>
   <si>
-    <t>階層的にカテゴリーを設定することで粒度のレベルを概念定義できる。</t>
+    <t>必要なカテゴリバリューセットに加えて、この要素は、所有者のカテゴリの定義に基づいてさまざまな分類スキームを許可し、効果的に複数のカテゴリを一度に使用できます。粒度のレベルは、値セットのカテゴリの概念によって定義されます。 / In addition to the required category valueset, this element allows various categorization schemes based on the owner’s definition of the category and effectively multiple categories can be used at once.  The level of granularity is defined by the category concepts in the value set.</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS</t>
   </si>
   <si>
     <t>Observation.category:first.id</t>
@@ -927,10 +933,10 @@
     <t>second</t>
   </si>
   <si>
-    <t>このObservationに関するLOINC上の分類、必須項目</t>
-  </si>
-  <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationDentalCategory_VS</t>
+    <t>第2カテゴリはLOINCのコードLP89803-8固定とする、ValueSetのバインディングを指定していないことに注意すること</t>
+  </si>
+  <si>
+    <t>階層的にカテゴリーを設定することで粒度のレベルを概念定義できる。</t>
   </si>
   <si>
     <t>Observation.category:second.id</t>
@@ -3994,15 +4000,17 @@
       <c r="X16" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="Y16" s="2"/>
+      <c r="Y16" t="s" s="2">
+        <v>202</v>
+      </c>
       <c r="Z16" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AC16" s="2"/>
       <c r="AD16" t="s" s="2">
@@ -4036,10 +4044,10 @@
         <v>83</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>83</v>
@@ -4047,13 +4055,13 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B17" t="s" s="2">
         <v>196</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D17" t="s" s="2">
         <v>83</v>
@@ -4063,7 +4071,7 @@
         <v>94</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>83</v>
@@ -4078,13 +4086,13 @@
         <v>198</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="O17" t="s" s="2">
         <v>201</v>
@@ -4116,7 +4124,7 @@
       </c>
       <c r="Y17" s="2"/>
       <c r="Z17" t="s" s="2">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>83</v>
@@ -4158,10 +4166,10 @@
         <v>83</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>83</v>
@@ -4169,10 +4177,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4195,13 +4203,13 @@
         <v>83</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4252,7 +4260,7 @@
         <v>83</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4276,7 +4284,7 @@
         <v>83</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>83</v>
@@ -4287,10 +4295,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4316,10 +4324,10 @@
         <v>139</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="N19" t="s" s="2">
         <v>156</v>
@@ -4363,7 +4371,7 @@
         <v>142</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>83</v>
@@ -4372,7 +4380,7 @@
         <v>143</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4396,7 +4404,7 @@
         <v>83</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>83</v>
@@ -4407,10 +4415,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4433,19 +4441,19 @@
         <v>95</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>83</v>
@@ -4494,7 +4502,7 @@
         <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4515,10 +4523,10 @@
         <v>83</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>83</v>
@@ -4529,10 +4537,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4555,13 +4563,13 @@
         <v>83</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4612,7 +4620,7 @@
         <v>83</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4636,7 +4644,7 @@
         <v>83</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>83</v>
@@ -4647,10 +4655,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4676,10 +4684,10 @@
         <v>139</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="N22" t="s" s="2">
         <v>156</v>
@@ -4723,7 +4731,7 @@
         <v>142</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>83</v>
@@ -4732,7 +4740,7 @@
         <v>143</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -4756,7 +4764,7 @@
         <v>83</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>83</v>
@@ -4767,10 +4775,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4796,23 +4804,23 @@
         <v>108</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="S23" t="s" s="2">
         <v>83</v>
@@ -4854,7 +4862,7 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -4875,10 +4883,10 @@
         <v>83</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>83</v>
@@ -4889,10 +4897,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4915,16 +4923,16 @@
         <v>95</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4974,7 +4982,7 @@
         <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -4995,10 +5003,10 @@
         <v>83</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>83</v>
@@ -5009,10 +5017,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5038,21 +5046,21 @@
         <v>114</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="S25" t="s" s="2">
         <v>83</v>
@@ -5094,7 +5102,7 @@
         <v>83</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -5115,10 +5123,10 @@
         <v>83</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>83</v>
@@ -5129,10 +5137,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5155,17 +5163,17 @@
         <v>95</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>83</v>
@@ -5214,7 +5222,7 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -5235,10 +5243,10 @@
         <v>83</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>83</v>
@@ -5249,10 +5257,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5275,19 +5283,19 @@
         <v>95</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>83</v>
@@ -5336,7 +5344,7 @@
         <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5357,10 +5365,10 @@
         <v>83</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>83</v>
@@ -5371,10 +5379,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5397,19 +5405,19 @@
         <v>95</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>83</v>
@@ -5458,7 +5466,7 @@
         <v>83</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -5479,10 +5487,10 @@
         <v>83</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>83</v>
@@ -5493,13 +5501,13 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B29" t="s" s="2">
         <v>196</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D29" t="s" s="2">
         <v>83</v>
@@ -5524,13 +5532,13 @@
         <v>198</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>209</v>
+        <v>296</v>
       </c>
       <c r="O29" t="s" s="2">
         <v>201</v>
@@ -5558,11 +5566,13 @@
         <v>83</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="Y29" s="2"/>
+        <v>118</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>202</v>
+      </c>
       <c r="Z29" t="s" s="2">
-        <v>294</v>
+        <v>203</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>83</v>
@@ -5604,10 +5614,10 @@
         <v>83</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>83</v>
@@ -5615,10 +5625,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5641,13 +5651,13 @@
         <v>83</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5698,7 +5708,7 @@
         <v>83</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5722,7 +5732,7 @@
         <v>83</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>83</v>
@@ -5733,10 +5743,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5762,10 +5772,10 @@
         <v>139</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="N31" t="s" s="2">
         <v>156</v>
@@ -5809,7 +5819,7 @@
         <v>142</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>83</v>
@@ -5818,7 +5828,7 @@
         <v>143</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5842,7 +5852,7 @@
         <v>83</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>83</v>
@@ -5853,10 +5863,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5879,19 +5889,19 @@
         <v>95</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>83</v>
@@ -5940,7 +5950,7 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5961,10 +5971,10 @@
         <v>83</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>83</v>
@@ -5975,10 +5985,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6001,13 +6011,13 @@
         <v>83</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6058,7 +6068,7 @@
         <v>83</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -6082,7 +6092,7 @@
         <v>83</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>83</v>
@@ -6093,10 +6103,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6122,10 +6132,10 @@
         <v>139</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="N34" t="s" s="2">
         <v>156</v>
@@ -6169,7 +6179,7 @@
         <v>142</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AD34" t="s" s="2">
         <v>83</v>
@@ -6178,7 +6188,7 @@
         <v>143</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6202,7 +6212,7 @@
         <v>83</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>83</v>
@@ -6213,10 +6223,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6242,23 +6252,23 @@
         <v>108</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>83</v>
@@ -6300,7 +6310,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6321,10 +6331,10 @@
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>83</v>
@@ -6335,10 +6345,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6361,16 +6371,16 @@
         <v>95</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6420,7 +6430,7 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6441,10 +6451,10 @@
         <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>83</v>
@@ -6455,10 +6465,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6484,21 +6494,21 @@
         <v>114</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>83</v>
@@ -6540,7 +6550,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6561,10 +6571,10 @@
         <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>83</v>
@@ -6575,10 +6585,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6601,17 +6611,17 @@
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>83</v>
@@ -6660,7 +6670,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6681,10 +6691,10 @@
         <v>83</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>83</v>
@@ -6695,10 +6705,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6721,19 +6731,19 @@
         <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>83</v>
@@ -6782,7 +6792,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6803,10 +6813,10 @@
         <v>83</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>83</v>
@@ -6817,10 +6827,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6843,19 +6853,19 @@
         <v>95</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>83</v>
@@ -6904,7 +6914,7 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -6925,10 +6935,10 @@
         <v>83</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>83</v>
@@ -6939,13 +6949,13 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>196</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D41" t="s" s="2">
         <v>83</v>
@@ -6970,13 +6980,13 @@
         <v>198</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>209</v>
+        <v>296</v>
       </c>
       <c r="O41" t="s" s="2">
         <v>201</v>
@@ -7008,7 +7018,7 @@
       </c>
       <c r="Y41" s="2"/>
       <c r="Z41" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>83</v>
@@ -7050,10 +7060,10 @@
         <v>83</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>83</v>
@@ -7061,10 +7071,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7087,13 +7097,13 @@
         <v>83</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7144,7 +7154,7 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7168,7 +7178,7 @@
         <v>83</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>83</v>
@@ -7179,10 +7189,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7208,10 +7218,10 @@
         <v>139</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>156</v>
@@ -7255,7 +7265,7 @@
         <v>142</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>83</v>
@@ -7264,7 +7274,7 @@
         <v>143</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7288,7 +7298,7 @@
         <v>83</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>83</v>
@@ -7299,10 +7309,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7325,19 +7335,19 @@
         <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>83</v>
@@ -7386,7 +7396,7 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7407,10 +7417,10 @@
         <v>83</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>83</v>
@@ -7421,10 +7431,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7447,13 +7457,13 @@
         <v>83</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7504,7 +7514,7 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7528,7 +7538,7 @@
         <v>83</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>83</v>
@@ -7539,10 +7549,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7568,10 +7578,10 @@
         <v>139</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>156</v>
@@ -7615,7 +7625,7 @@
         <v>142</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>83</v>
@@ -7624,7 +7634,7 @@
         <v>143</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7648,7 +7658,7 @@
         <v>83</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>83</v>
@@ -7659,10 +7669,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7688,23 +7698,23 @@
         <v>108</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="S47" t="s" s="2">
         <v>83</v>
@@ -7746,7 +7756,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7767,10 +7777,10 @@
         <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>83</v>
@@ -7781,10 +7791,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7807,16 +7817,16 @@
         <v>95</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7866,7 +7876,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7887,10 +7897,10 @@
         <v>83</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>83</v>
@@ -7901,10 +7911,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7930,21 +7940,21 @@
         <v>114</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="S49" t="s" s="2">
         <v>83</v>
@@ -7986,7 +7996,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8007,10 +8017,10 @@
         <v>83</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>83</v>
@@ -8021,10 +8031,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8047,17 +8057,17 @@
         <v>95</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8106,7 +8116,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8127,10 +8137,10 @@
         <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>83</v>
@@ -8141,10 +8151,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8167,19 +8177,19 @@
         <v>95</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>83</v>
@@ -8228,7 +8238,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8249,10 +8259,10 @@
         <v>83</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>83</v>
@@ -8263,10 +8273,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8289,19 +8299,19 @@
         <v>95</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8350,7 +8360,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8371,10 +8381,10 @@
         <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>83</v>
@@ -8385,14 +8395,14 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8414,16 +8424,16 @@
         <v>198</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>83</v>
@@ -8448,13 +8458,13 @@
         <v>83</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>83</v>
@@ -8472,7 +8482,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>94</v>
@@ -8487,30 +8497,30 @@
         <v>106</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8533,13 +8543,13 @@
         <v>83</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8590,7 +8600,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8614,7 +8624,7 @@
         <v>83</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>83</v>
@@ -8625,10 +8635,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8654,10 +8664,10 @@
         <v>139</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>156</v>
@@ -8701,7 +8711,7 @@
         <v>142</v>
       </c>
       <c r="AC55" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AD55" t="s" s="2">
         <v>83</v>
@@ -8710,7 +8720,7 @@
         <v>143</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8734,7 +8744,7 @@
         <v>83</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>83</v>
@@ -8745,10 +8755,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8771,19 +8781,19 @@
         <v>95</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>83</v>
@@ -8832,7 +8842,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8853,10 +8863,10 @@
         <v>83</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>83</v>
@@ -8867,10 +8877,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8893,13 +8903,13 @@
         <v>83</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8950,7 +8960,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -8974,7 +8984,7 @@
         <v>83</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>83</v>
@@ -8985,10 +8995,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9014,10 +9024,10 @@
         <v>139</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>156</v>
@@ -9061,7 +9071,7 @@
         <v>142</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>83</v>
@@ -9070,7 +9080,7 @@
         <v>143</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9094,7 +9104,7 @@
         <v>83</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>83</v>
@@ -9105,10 +9115,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9134,23 +9144,23 @@
         <v>108</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q59" s="2"/>
       <c r="R59" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="S59" t="s" s="2">
         <v>83</v>
@@ -9192,7 +9202,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9213,10 +9223,10 @@
         <v>83</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
@@ -9227,10 +9237,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9253,16 +9263,16 @@
         <v>95</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9312,7 +9322,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9333,10 +9343,10 @@
         <v>83</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>83</v>
@@ -9347,10 +9357,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9376,21 +9386,21 @@
         <v>114</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q61" s="2"/>
       <c r="R61" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="S61" t="s" s="2">
         <v>83</v>
@@ -9432,7 +9442,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9453,10 +9463,10 @@
         <v>83</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>83</v>
@@ -9467,10 +9477,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9493,17 +9503,17 @@
         <v>95</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -9513,7 +9523,7 @@
         <v>83</v>
       </c>
       <c r="S62" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="T62" t="s" s="2">
         <v>83</v>
@@ -9552,7 +9562,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9573,10 +9583,10 @@
         <v>83</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>83</v>
@@ -9587,10 +9597,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9613,19 +9623,19 @@
         <v>95</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -9674,7 +9684,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9695,10 +9705,10 @@
         <v>83</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>83</v>
@@ -9709,10 +9719,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9735,19 +9745,19 @@
         <v>95</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
@@ -9796,7 +9806,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9817,10 +9827,10 @@
         <v>83</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>83</v>
@@ -9831,10 +9841,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9857,19 +9867,19 @@
         <v>95</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>83</v>
@@ -9918,7 +9928,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -9933,19 +9943,19 @@
         <v>106</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>83</v>
@@ -9953,10 +9963,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9979,7 +9989,7 @@
         <v>95</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="L66" t="s" s="2">
         <v>179</v>
@@ -9988,7 +9998,7 @@
         <v>179</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10038,7 +10048,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10059,13 +10069,13 @@
         <v>83</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>83</v>
@@ -10073,14 +10083,14 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10099,19 +10109,19 @@
         <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
@@ -10160,7 +10170,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10175,19 +10185,19 @@
         <v>106</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>83</v>
@@ -10195,14 +10205,14 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -10221,19 +10231,19 @@
         <v>95</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>83</v>
@@ -10282,7 +10292,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10297,19 +10307,19 @@
         <v>106</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>83</v>
@@ -10317,10 +10327,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10343,16 +10353,16 @@
         <v>95</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10402,7 +10412,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10423,13 +10433,13 @@
         <v>83</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>83</v>
@@ -10437,10 +10447,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10463,19 +10473,19 @@
         <v>95</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>83</v>
@@ -10524,7 +10534,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10539,19 +10549,19 @@
         <v>106</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>83</v>
@@ -10559,10 +10569,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10588,16 +10598,16 @@
         <v>198</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>83</v>
@@ -10626,7 +10636,7 @@
       </c>
       <c r="Y71" s="2"/>
       <c r="Z71" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>83</v>
@@ -10644,7 +10654,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10653,7 +10663,7 @@
         <v>94</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>106</v>
@@ -10662,27 +10672,27 @@
         <v>83</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10708,16 +10718,16 @@
         <v>198</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>83</v>
@@ -10742,13 +10752,13 @@
         <v>83</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>83</v>
@@ -10766,7 +10776,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -10775,7 +10785,7 @@
         <v>94</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>106</v>
@@ -10790,7 +10800,7 @@
         <v>137</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>83</v>
@@ -10801,14 +10811,14 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -10836,10 +10846,10 @@
         <v>179</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>83</v>
@@ -10864,13 +10874,13 @@
         <v>83</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>83</v>
@@ -10888,7 +10898,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -10906,27 +10916,27 @@
         <v>83</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10949,7 +10959,7 @@
         <v>83</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="L74" t="s" s="2">
         <v>179</v>
@@ -10958,10 +10968,10 @@
         <v>179</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>83</v>
@@ -11010,7 +11020,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11031,10 +11041,10 @@
         <v>83</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>83</v>
@@ -11045,10 +11055,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11074,13 +11084,13 @@
         <v>198</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11110,7 +11120,7 @@
       </c>
       <c r="Y75" s="2"/>
       <c r="Z75" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>83</v>
@@ -11128,7 +11138,7 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11146,27 +11156,27 @@
         <v>83</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11192,16 +11202,16 @@
         <v>198</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>83</v>
@@ -11226,13 +11236,13 @@
         <v>83</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>83</v>
@@ -11250,7 +11260,7 @@
         <v>83</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11271,10 +11281,10 @@
         <v>83</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>83</v>
@@ -11285,10 +11295,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11311,7 +11321,7 @@
         <v>83</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="L77" t="s" s="2">
         <v>179</v>
@@ -11320,7 +11330,7 @@
         <v>179</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11370,7 +11380,7 @@
         <v>83</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11388,27 +11398,27 @@
         <v>83</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11431,16 +11441,16 @@
         <v>83</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11490,7 +11500,7 @@
         <v>83</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11508,27 +11518,27 @@
         <v>83</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11551,7 +11561,7 @@
         <v>83</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="L79" t="s" s="2">
         <v>179</v>
@@ -11560,10 +11570,10 @@
         <v>179</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>83</v>
@@ -11612,7 +11622,7 @@
         <v>83</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -11624,7 +11634,7 @@
         <v>83</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>83</v>
@@ -11633,10 +11643,10 @@
         <v>83</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>83</v>
@@ -11647,10 +11657,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11673,13 +11683,13 @@
         <v>83</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11730,7 +11740,7 @@
         <v>83</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -11754,7 +11764,7 @@
         <v>83</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>83</v>
@@ -11765,10 +11775,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11794,10 +11804,10 @@
         <v>139</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="N81" t="s" s="2">
         <v>156</v>
@@ -11850,7 +11860,7 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -11874,7 +11884,7 @@
         <v>83</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>83</v>
@@ -11885,14 +11895,14 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -11914,10 +11924,10 @@
         <v>139</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="N82" t="s" s="2">
         <v>156</v>
@@ -11972,7 +11982,7 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -12007,10 +12017,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12033,13 +12043,13 @@
         <v>83</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -12090,7 +12100,7 @@
         <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12099,7 +12109,7 @@
         <v>94</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>106</v>
@@ -12111,10 +12121,10 @@
         <v>83</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>83</v>
@@ -12125,10 +12135,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12151,13 +12161,13 @@
         <v>83</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -12208,7 +12218,7 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12217,7 +12227,7 @@
         <v>94</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="AJ84" t="s" s="2">
         <v>106</v>
@@ -12229,10 +12239,10 @@
         <v>83</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>83</v>
@@ -12243,10 +12253,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12272,16 +12282,16 @@
         <v>198</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>83</v>
@@ -12309,10 +12319,10 @@
         <v>118</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>83</v>
@@ -12330,7 +12340,7 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12348,13 +12358,13 @@
         <v>83</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>83</v>
@@ -12365,10 +12375,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12394,16 +12404,16 @@
         <v>198</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>83</v>
@@ -12428,13 +12438,13 @@
         <v>83</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>83</v>
@@ -12452,7 +12462,7 @@
         <v>83</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -12470,13 +12480,13 @@
         <v>83</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>83</v>
@@ -12487,10 +12497,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12513,17 +12523,17 @@
         <v>83</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>83</v>
@@ -12572,7 +12582,7 @@
         <v>83</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -12596,7 +12606,7 @@
         <v>83</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>83</v>
@@ -12607,10 +12617,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12633,13 +12643,13 @@
         <v>83</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12690,7 +12700,7 @@
         <v>83</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -12711,10 +12721,10 @@
         <v>83</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>83</v>
@@ -12725,10 +12735,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12751,16 +12761,16 @@
         <v>95</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -12810,7 +12820,7 @@
         <v>83</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -12831,10 +12841,10 @@
         <v>83</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>83</v>
@@ -12845,10 +12855,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12871,7 +12881,7 @@
         <v>95</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="L90" t="s" s="2">
         <v>179</v>
@@ -12880,7 +12890,7 @@
         <v>179</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -12930,7 +12940,7 @@
         <v>83</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -12951,10 +12961,10 @@
         <v>83</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>83</v>
@@ -12965,10 +12975,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12991,7 +13001,7 @@
         <v>95</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="L91" t="s" s="2">
         <v>179</v>
@@ -13000,10 +13010,10 @@
         <v>179</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>83</v>
@@ -13052,7 +13062,7 @@
         <v>83</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -13073,10 +13083,10 @@
         <v>83</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>83</v>
@@ -13087,10 +13097,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13113,13 +13123,13 @@
         <v>83</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -13170,7 +13180,7 @@
         <v>83</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -13194,7 +13204,7 @@
         <v>83</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>83</v>
@@ -13205,10 +13215,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13234,10 +13244,10 @@
         <v>139</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="N93" t="s" s="2">
         <v>156</v>
@@ -13290,7 +13300,7 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -13314,7 +13324,7 @@
         <v>83</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>83</v>
@@ -13325,14 +13335,14 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
@@ -13354,10 +13364,10 @@
         <v>139</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="N94" t="s" s="2">
         <v>156</v>
@@ -13412,7 +13422,7 @@
         <v>83</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -13447,10 +13457,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13476,16 +13486,16 @@
         <v>198</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>83</v>
@@ -13510,13 +13520,13 @@
         <v>83</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>83</v>
@@ -13534,7 +13544,7 @@
         <v>83</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>94</v>
@@ -13552,16 +13562,16 @@
         <v>83</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AP95" t="s" s="2">
         <v>83</v>
@@ -13569,10 +13579,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13595,19 +13605,19 @@
         <v>95</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>83</v>
@@ -13656,7 +13666,7 @@
         <v>83</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
@@ -13674,27 +13684,27 @@
         <v>83</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13720,16 +13730,16 @@
         <v>198</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>83</v>
@@ -13754,13 +13764,13 @@
         <v>83</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>83</v>
@@ -13778,7 +13788,7 @@
         <v>83</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
@@ -13787,7 +13797,7 @@
         <v>94</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AJ97" t="s" s="2">
         <v>106</v>
@@ -13802,7 +13812,7 @@
         <v>137</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>83</v>
@@ -13813,14 +13823,14 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
@@ -13842,16 +13852,16 @@
         <v>198</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>83</v>
@@ -13876,13 +13886,13 @@
         <v>83</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>83</v>
@@ -13900,7 +13910,7 @@
         <v>83</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -13918,27 +13928,27 @@
         <v>83</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP98" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13964,16 +13974,16 @@
         <v>84</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>83</v>
@@ -14022,7 +14032,7 @@
         <v>83</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>81</v>
@@ -14043,10 +14053,10 @@
         <v>83</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>83</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
@@ -933,7 +933,7 @@
     <t>second</t>
   </si>
   <si>
-    <t>第2カテゴリはLOINCのコードLP89803-8固定とする、ValueSetのバインディングを指定していないことに注意すること</t>
+    <t>第2カテゴリはLOINCのコードLP89803-8固定で必須とする、ValueSetは指定しない</t>
   </si>
   <si>
     <t>階層的にカテゴリーを設定することで粒度のレベルを概念定義できる。</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-dev</t>
+    <t>1.3.0-dev</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-18</t>
+    <t>2024-12-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
@@ -282,7 +282,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}obs-6:databsentrasonは、観察.value [x]が存在しない場合にのみ存在するものとします / dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:visserveration.codeがvisserveration.component.codeと同じ場合、コードに関連付けられている値要素が存在しないでください / If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReasonは、Observation.value [x]が存在しない場合にのみ存在するものとします / dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:Observation.codeがObservation.component.codeと同じ場合、そのcodeに関連付くvalueは存在してはならない。 / If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -1315,7 +1315,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>結果（ `balue.value [x]`）が欠落している理由を指定するコード。 / Codes specifying why the result (`Observation.value[x]`) is missing.</t>
+    <t>結果（ `Observation.value[x]`）が欠落している理由を指定するコード。 / Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
@@ -1490,7 +1490,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-obs-3:少なくとも低いまたは高またはテキストが必要です / Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
+obs-3:少なくともlow, high, textのいずれかが必要です / Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
   </si>
   <si>
     <t>OBX.7</t>
@@ -1744,7 +1744,7 @@
   </si>
   <si>
     <t>「null」または例外的な値は、FHIR観測で2つの方法を表すことができます。1つの方法は、それらを単に値セットに含めるだけで、値の例外を表すことです。たとえば、血清学テストの測定値は、「検出」、「検出されない」、「決定的でない」、または「テストなし」です。
-別の方法は、実際の観測に値要素を使用し、明示的なDataBsEntreason要素を使用して例外的な値を記録することです。たとえば、測定が完了していないときに、DataBsentrasonコード「エラー」を使用できます。これらのオプションのため、一般的な観測を例外的な価値のために解釈するには、ユースケース契約が必要です。 / "Null" or exceptional values can be represented two ways in FHIR Observations.  One way is to simply include them in the value set and represent the exceptions in the value.  For example, measurement values for a serology test could be  "detected", "not detected", "inconclusive", or  "test not done". 
+別の方法は、実際の観測に値要素を使用し、明示的なDataBsEntreason要素を使用して例外的な値を記録することです。たとえば、測定が完了していないときに、dataAbsentReasonコード「エラー」を使用できます。これらのオプションのため、一般的な観測を例外的な価値のために解釈するには、ユースケース契約が必要です。 / "Null" or exceptional values can be represented two ways in FHIR Observations.  One way is to simply include them in the value set and represent the exceptions in the value.  For example, measurement values for a serology test could be  "detected", "not detected", "inconclusive", or  "test not done". 
 The alternate way is to use the value element for actual observations and use the explicit dataAbsentReason element to record exceptional values.  For example, the dataAbsentReason code "error" could be used when the measurement was not completed.  Because of these options, use-case agreements are required to interpret general observations for exceptional values.</t>
   </si>
   <si>
@@ -2106,7 +2106,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="105.8828125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="111.37890625" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="70.58203125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
@@ -1561,7 +1561,7 @@
     <t>Observation.referenceRange.type</t>
   </si>
   <si>
-    <t>参照範囲予選 / Reference range qualifier</t>
+    <t>参照範囲予選修飾子 / Reference range qualifier</t>
   </si>
   <si>
     <t>適用されるターゲット参照母集団のどの部分を示すコード。たとえば、通常または治療範囲。 / Codes to indicate the what part of the targeted reference population it applies to. For example, the normal or therapeutic range.</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3830" uniqueCount="564">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4021" uniqueCount="569">
   <si>
     <t>Property</t>
   </si>
@@ -641,9 +641,9 @@
     <t>このObservationを分類するコード</t>
   </si>
   <si>
-    <t>3つのコードを設定する。
-第1コード（first）は、simpleObservationコード体系を必須とし、procedureを設定する。
-第2コード（second）は、歯科を表すコードLP89803-8を設定する。
+    <t>3つのコードを設定する。
+第1コード（first）は、simpleObservationコード体系を必須とし、procedureを設定する。
+第2コード（second）は、歯科を表すコードLP89803-8を設定する。
 第3コード（third）は、歯の有無や処置状態などを表すコードを設定する。なお、日本では適切なコード体系が存在しないため、独自のバリューセットを定義する。</t>
   </si>
   <si>
@@ -1385,8 +1385,8 @@
     <t>特定の歯（歯式）</t>
   </si>
   <si>
-    <t>優先順位は以下の番号を推奨する。
-1.FDI
+    <t>優先順位は以下の番号を推奨する。
+1.FDI
 2.厚生労働省標準標準歯式マスタ、レセプト電算処理用コード</t>
   </si>
   <si>
@@ -1403,6 +1403,21 @@
   </si>
   <si>
     <t>718497002 |Inherent location|</t>
+  </si>
+  <si>
+    <t>Observation.bodySite.id</t>
+  </si>
+  <si>
+    <t>Observation.bodySite.extension</t>
+  </si>
+  <si>
+    <t>Observation.bodySite.extension:bodySiteStatus</t>
+  </si>
+  <si>
+    <t>Observation.bodySite.coding</t>
+  </si>
+  <si>
+    <t>Observation.bodySite.text</t>
   </si>
   <si>
     <t>Observation.method</t>
@@ -2079,7 +2094,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP99"/>
+  <dimension ref="A1:AP104"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="47.2890625" customWidth="true" bestFit="true"/>
@@ -11199,20 +11214,16 @@
         <v>83</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>198</v>
+        <v>214</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>448</v>
+        <v>215</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>450</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="N76" s="2"/>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>83</v>
       </c>
@@ -11236,13 +11247,13 @@
         <v>83</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>332</v>
+        <v>83</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>451</v>
+        <v>83</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>452</v>
+        <v>83</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>83</v>
@@ -11260,7 +11271,7 @@
         <v>83</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>447</v>
+        <v>217</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11272,7 +11283,7 @@
         <v>83</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>83</v>
@@ -11281,10 +11292,10 @@
         <v>83</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>453</v>
+        <v>83</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>454</v>
+        <v>218</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>83</v>
@@ -11295,21 +11306,21 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>83</v>
+        <v>153</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>83</v>
@@ -11321,16 +11332,16 @@
         <v>83</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>456</v>
+        <v>139</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>179</v>
+        <v>221</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>179</v>
+        <v>222</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>457</v>
+        <v>156</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11368,59 +11379,61 @@
         <v>83</v>
       </c>
       <c r="AB77" t="s" s="2">
-        <v>83</v>
+        <v>142</v>
       </c>
       <c r="AC77" t="s" s="2">
-        <v>83</v>
+        <v>223</v>
       </c>
       <c r="AD77" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE77" t="s" s="2">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>455</v>
+        <v>224</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>458</v>
+        <v>83</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>459</v>
+        <v>83</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>460</v>
+        <v>218</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>461</v>
+        <v>83</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>462</v>
+        <v>449</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="C78" s="2"/>
+        <v>448</v>
+      </c>
+      <c r="C78" t="s" s="2">
+        <v>147</v>
+      </c>
       <c r="D78" t="s" s="2">
         <v>83</v>
       </c>
@@ -11429,7 +11442,7 @@
         <v>81</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>83</v>
@@ -11441,17 +11454,15 @@
         <v>83</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>463</v>
+        <v>148</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>464</v>
+        <v>149</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>465</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="N78" s="2"/>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>83</v>
@@ -11500,45 +11511,45 @@
         <v>83</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>462</v>
+        <v>224</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>466</v>
+        <v>83</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>467</v>
+        <v>83</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>468</v>
+        <v>83</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>469</v>
+        <v>83</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>470</v>
+        <v>450</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>470</v>
+        <v>450</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11558,22 +11569,22 @@
         <v>83</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>471</v>
+        <v>227</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>179</v>
+        <v>228</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>179</v>
+        <v>229</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>472</v>
+        <v>230</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>473</v>
+        <v>231</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>83</v>
@@ -11622,7 +11633,7 @@
         <v>83</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>470</v>
+        <v>232</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -11634,7 +11645,7 @@
         <v>83</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>474</v>
+        <v>106</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>83</v>
@@ -11643,10 +11654,10 @@
         <v>83</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>475</v>
+        <v>233</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>476</v>
+        <v>234</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>83</v>
@@ -11657,10 +11668,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>477</v>
+        <v>451</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>477</v>
+        <v>451</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11680,19 +11691,23 @@
         <v>83</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K80" t="s" s="2">
         <v>214</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>215</v>
+        <v>286</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N80" s="2"/>
-      <c r="O80" s="2"/>
+        <v>287</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="O80" t="s" s="2">
+        <v>289</v>
+      </c>
       <c r="P80" t="s" s="2">
         <v>83</v>
       </c>
@@ -11740,7 +11755,7 @@
         <v>83</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>217</v>
+        <v>290</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -11752,7 +11767,7 @@
         <v>83</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>83</v>
@@ -11761,10 +11776,10 @@
         <v>83</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>83</v>
+        <v>291</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>218</v>
+        <v>292</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>83</v>
@@ -11775,21 +11790,21 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>478</v>
+        <v>452</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>478</v>
+        <v>452</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>153</v>
+        <v>83</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>83</v>
@@ -11801,18 +11816,20 @@
         <v>83</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>139</v>
+        <v>198</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>221</v>
+        <v>453</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>222</v>
+        <v>453</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="O81" s="2"/>
+        <v>454</v>
+      </c>
+      <c r="O81" t="s" s="2">
+        <v>455</v>
+      </c>
       <c r="P81" t="s" s="2">
         <v>83</v>
       </c>
@@ -11836,13 +11853,13 @@
         <v>83</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>83</v>
+        <v>332</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>83</v>
+        <v>456</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>83</v>
+        <v>457</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>83</v>
@@ -11860,19 +11877,19 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>224</v>
+        <v>452</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>83</v>
@@ -11881,10 +11898,10 @@
         <v>83</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>83</v>
+        <v>458</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>218</v>
+        <v>459</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>83</v>
@@ -11895,46 +11912,44 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>479</v>
+        <v>460</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>479</v>
+        <v>460</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>480</v>
+        <v>83</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I82" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>139</v>
+        <v>461</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>481</v>
+        <v>179</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>482</v>
+        <v>179</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>157</v>
-      </c>
+        <v>462</v>
+      </c>
+      <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>83</v>
       </c>
@@ -11982,45 +11997,45 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>483</v>
+        <v>460</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>83</v>
+        <v>463</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>83</v>
+        <v>464</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>137</v>
+        <v>465</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>83</v>
+        <v>466</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>484</v>
+        <v>467</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>484</v>
+        <v>467</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12043,15 +12058,17 @@
         <v>83</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>485</v>
+        <v>468</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>486</v>
+        <v>469</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="N83" s="2"/>
+        <v>469</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>470</v>
+      </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>83</v>
@@ -12100,7 +12117,7 @@
         <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>484</v>
+        <v>467</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12109,7 +12126,7 @@
         <v>94</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>488</v>
+        <v>83</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>106</v>
@@ -12118,27 +12135,27 @@
         <v>83</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>83</v>
+        <v>471</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>489</v>
+        <v>472</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>490</v>
+        <v>473</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>83</v>
+        <v>474</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>491</v>
+        <v>475</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>491</v>
+        <v>475</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12149,7 +12166,7 @@
         <v>81</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>83</v>
@@ -12161,16 +12178,20 @@
         <v>83</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>492</v>
+        <v>179</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="N84" s="2"/>
-      <c r="O84" s="2"/>
+        <v>179</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>478</v>
+      </c>
       <c r="P84" t="s" s="2">
         <v>83</v>
       </c>
@@ -12218,19 +12239,19 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>491</v>
+        <v>475</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>488</v>
+        <v>83</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>106</v>
+        <v>479</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>83</v>
@@ -12239,10 +12260,10 @@
         <v>83</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>489</v>
+        <v>480</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>494</v>
+        <v>481</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>83</v>
@@ -12253,10 +12274,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>495</v>
+        <v>482</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>495</v>
+        <v>482</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12279,20 +12300,16 @@
         <v>83</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>198</v>
+        <v>214</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>496</v>
+        <v>215</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>499</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="N85" s="2"/>
+      <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>83</v>
       </c>
@@ -12316,13 +12333,13 @@
         <v>83</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>500</v>
+        <v>83</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>501</v>
+        <v>83</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>83</v>
@@ -12340,7 +12357,7 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>495</v>
+        <v>217</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12352,19 +12369,19 @@
         <v>83</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>502</v>
+        <v>83</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>503</v>
+        <v>83</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>431</v>
+        <v>218</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>83</v>
@@ -12375,14 +12392,14 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>504</v>
+        <v>483</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>504</v>
+        <v>483</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>83</v>
+        <v>153</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
@@ -12401,20 +12418,18 @@
         <v>83</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>198</v>
+        <v>139</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>505</v>
+        <v>221</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>506</v>
+        <v>222</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>508</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>83</v>
       </c>
@@ -12438,13 +12453,13 @@
         <v>83</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>332</v>
+        <v>83</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>509</v>
+        <v>83</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>510</v>
+        <v>83</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>83</v>
@@ -12462,7 +12477,7 @@
         <v>83</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>504</v>
+        <v>224</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -12474,19 +12489,19 @@
         <v>83</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>502</v>
+        <v>83</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>503</v>
+        <v>83</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>431</v>
+        <v>218</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>83</v>
@@ -12497,43 +12512,45 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>511</v>
+        <v>484</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>511</v>
+        <v>484</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>83</v>
+        <v>485</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I87" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>512</v>
+        <v>139</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>513</v>
+        <v>486</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="N87" s="2"/>
+        <v>487</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>156</v>
+      </c>
       <c r="O87" t="s" s="2">
-        <v>515</v>
+        <v>157</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>83</v>
@@ -12582,19 +12599,19 @@
         <v>83</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>511</v>
+        <v>488</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>83</v>
@@ -12606,7 +12623,7 @@
         <v>83</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>516</v>
+        <v>137</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>83</v>
@@ -12617,10 +12634,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>517</v>
+        <v>489</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>517</v>
+        <v>489</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12643,13 +12660,13 @@
         <v>83</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>214</v>
+        <v>490</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>518</v>
+        <v>491</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>519</v>
+        <v>492</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12700,7 +12717,7 @@
         <v>83</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>517</v>
+        <v>489</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -12709,7 +12726,7 @@
         <v>94</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>83</v>
+        <v>493</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>106</v>
@@ -12721,10 +12738,10 @@
         <v>83</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>520</v>
+        <v>495</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>83</v>
@@ -12735,10 +12752,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>521</v>
+        <v>496</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>521</v>
+        <v>496</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12749,7 +12766,7 @@
         <v>81</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>83</v>
@@ -12758,20 +12775,18 @@
         <v>83</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>522</v>
+        <v>490</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>523</v>
+        <v>497</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>524</v>
-      </c>
+        <v>498</v>
+      </c>
+      <c r="N89" s="2"/>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>83</v>
@@ -12820,16 +12835,16 @@
         <v>83</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>521</v>
+        <v>496</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>83</v>
+        <v>493</v>
       </c>
       <c r="AJ89" t="s" s="2">
         <v>106</v>
@@ -12841,10 +12856,10 @@
         <v>83</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>525</v>
+        <v>494</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>526</v>
+        <v>499</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>83</v>
@@ -12855,10 +12870,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>527</v>
+        <v>500</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>527</v>
+        <v>500</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12869,7 +12884,7 @@
         <v>81</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>83</v>
@@ -12878,21 +12893,23 @@
         <v>83</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>528</v>
+        <v>198</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>179</v>
+        <v>501</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>179</v>
+        <v>502</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="O90" s="2"/>
+        <v>503</v>
+      </c>
+      <c r="O90" t="s" s="2">
+        <v>504</v>
+      </c>
       <c r="P90" t="s" s="2">
         <v>83</v>
       </c>
@@ -12916,13 +12933,13 @@
         <v>83</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>83</v>
+        <v>505</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>83</v>
+        <v>506</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>83</v>
@@ -12940,13 +12957,13 @@
         <v>83</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>527</v>
+        <v>500</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>83</v>
@@ -12958,13 +12975,13 @@
         <v>83</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>83</v>
+        <v>507</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>525</v>
+        <v>508</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>530</v>
+        <v>431</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>83</v>
@@ -12975,10 +12992,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>531</v>
+        <v>509</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>531</v>
+        <v>509</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12998,22 +13015,22 @@
         <v>83</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>471</v>
+        <v>198</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>179</v>
+        <v>510</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>179</v>
+        <v>511</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>532</v>
+        <v>512</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>533</v>
+        <v>513</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>83</v>
@@ -13038,13 +13055,13 @@
         <v>83</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>83</v>
+        <v>332</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>83</v>
+        <v>514</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>83</v>
+        <v>515</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>83</v>
@@ -13062,7 +13079,7 @@
         <v>83</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>531</v>
+        <v>509</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -13080,13 +13097,13 @@
         <v>83</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>83</v>
+        <v>507</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>534</v>
+        <v>508</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>535</v>
+        <v>431</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>83</v>
@@ -13097,10 +13114,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>536</v>
+        <v>516</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>536</v>
+        <v>516</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13123,16 +13140,18 @@
         <v>83</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>214</v>
+        <v>517</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>215</v>
+        <v>518</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>216</v>
+        <v>519</v>
       </c>
       <c r="N92" s="2"/>
-      <c r="O92" s="2"/>
+      <c r="O92" t="s" s="2">
+        <v>520</v>
+      </c>
       <c r="P92" t="s" s="2">
         <v>83</v>
       </c>
@@ -13180,7 +13199,7 @@
         <v>83</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>217</v>
+        <v>516</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -13192,7 +13211,7 @@
         <v>83</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>83</v>
@@ -13204,7 +13223,7 @@
         <v>83</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>218</v>
+        <v>521</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>83</v>
@@ -13215,21 +13234,21 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>537</v>
+        <v>522</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>537</v>
+        <v>522</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>153</v>
+        <v>83</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>83</v>
@@ -13241,17 +13260,15 @@
         <v>83</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>139</v>
+        <v>214</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>221</v>
+        <v>523</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>156</v>
-      </c>
+        <v>524</v>
+      </c>
+      <c r="N93" s="2"/>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>83</v>
@@ -13300,19 +13317,19 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>224</v>
+        <v>522</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>83</v>
@@ -13321,10 +13338,10 @@
         <v>83</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>83</v>
+        <v>494</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>218</v>
+        <v>525</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>83</v>
@@ -13335,14 +13352,14 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>538</v>
+        <v>526</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>538</v>
+        <v>526</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>480</v>
+        <v>83</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
@@ -13355,26 +13372,24 @@
         <v>83</v>
       </c>
       <c r="I94" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J94" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>139</v>
+        <v>527</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>481</v>
+        <v>528</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>482</v>
+        <v>528</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>157</v>
-      </c>
+        <v>529</v>
+      </c>
+      <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>83</v>
       </c>
@@ -13422,7 +13437,7 @@
         <v>83</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>483</v>
+        <v>526</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -13434,7 +13449,7 @@
         <v>83</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>83</v>
@@ -13443,10 +13458,10 @@
         <v>83</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>83</v>
+        <v>530</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>137</v>
+        <v>531</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>83</v>
@@ -13457,10 +13472,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>539</v>
+        <v>532</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>539</v>
+        <v>532</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13468,10 +13483,10 @@
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>83</v>
@@ -13483,20 +13498,18 @@
         <v>95</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>198</v>
+        <v>533</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>540</v>
+        <v>179</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>541</v>
+        <v>179</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="O95" t="s" s="2">
-        <v>331</v>
-      </c>
+        <v>534</v>
+      </c>
+      <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>83</v>
       </c>
@@ -13520,13 +13533,13 @@
         <v>83</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>332</v>
+        <v>83</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>333</v>
+        <v>83</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>334</v>
+        <v>83</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>83</v>
@@ -13544,13 +13557,13 @@
         <v>83</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>539</v>
+        <v>532</v>
       </c>
       <c r="AG95" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>83</v>
@@ -13562,16 +13575,16 @@
         <v>83</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>543</v>
+        <v>83</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>337</v>
+        <v>530</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>338</v>
+        <v>535</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>339</v>
+        <v>83</v>
       </c>
       <c r="AP95" t="s" s="2">
         <v>83</v>
@@ -13579,10 +13592,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13593,7 +13606,7 @@
         <v>81</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>83</v>
@@ -13605,19 +13618,19 @@
         <v>95</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>545</v>
+        <v>476</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>546</v>
+        <v>179</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>547</v>
+        <v>179</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>548</v>
+        <v>537</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>407</v>
+        <v>538</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>83</v>
@@ -13666,13 +13679,13 @@
         <v>83</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>83</v>
@@ -13684,27 +13697,27 @@
         <v>83</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>549</v>
+        <v>83</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>411</v>
+        <v>539</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>412</v>
+        <v>540</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>413</v>
+        <v>83</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>550</v>
+        <v>541</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>550</v>
+        <v>541</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13727,20 +13740,16 @@
         <v>83</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>198</v>
+        <v>214</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>551</v>
+        <v>215</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>417</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="N97" s="2"/>
+      <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>83</v>
       </c>
@@ -13764,13 +13773,13 @@
         <v>83</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>418</v>
+        <v>83</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>419</v>
+        <v>83</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>420</v>
+        <v>83</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>83</v>
@@ -13788,7 +13797,7 @@
         <v>83</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>550</v>
+        <v>217</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
@@ -13797,10 +13806,10 @@
         <v>94</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>421</v>
+        <v>83</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>83</v>
@@ -13809,10 +13818,10 @@
         <v>83</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>137</v>
+        <v>83</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>422</v>
+        <v>218</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>83</v>
@@ -13823,14 +13832,14 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>554</v>
+        <v>542</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>554</v>
+        <v>542</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>424</v>
+        <v>153</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
@@ -13849,20 +13858,18 @@
         <v>83</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>198</v>
+        <v>139</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>555</v>
+        <v>221</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>556</v>
+        <v>222</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>558</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>83</v>
       </c>
@@ -13886,13 +13893,13 @@
         <v>83</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>418</v>
+        <v>83</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>427</v>
+        <v>83</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>428</v>
+        <v>83</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>83</v>
@@ -13910,7 +13917,7 @@
         <v>83</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>554</v>
+        <v>224</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -13922,37 +13929,37 @@
         <v>83</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>429</v>
+        <v>83</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>430</v>
+        <v>83</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>431</v>
+        <v>218</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP98" t="s" s="2">
-        <v>432</v>
+        <v>83</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>559</v>
+        <v>543</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>559</v>
+        <v>543</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>83</v>
+        <v>485</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -13965,25 +13972,25 @@
         <v>83</v>
       </c>
       <c r="I99" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>560</v>
+        <v>486</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>561</v>
+        <v>487</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>562</v>
+        <v>156</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>563</v>
+        <v>157</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>83</v>
@@ -14032,7 +14039,7 @@
         <v>83</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>559</v>
+        <v>488</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>81</v>
@@ -14044,24 +14051,634 @@
         <v>83</v>
       </c>
       <c r="AJ99" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN99" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AO99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP99" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="C100" s="2"/>
+      <c r="D100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E100" s="2"/>
+      <c r="F100" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G100" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J100" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K100" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="L100" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="M100" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="O100" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="P100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q100" s="2"/>
+      <c r="R100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X100" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="Z100" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AA100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF100" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="AG100" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AH100" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ100" t="s" s="2">
         <v>106</v>
       </c>
-      <c r="AK99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM99" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="AN99" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="AO99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP99" t="s" s="2">
+      <c r="AK100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL100" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="AM100" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AN100" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="AO100" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="AP100" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="C101" s="2"/>
+      <c r="D101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E101" s="2"/>
+      <c r="F101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G101" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J101" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K101" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="L101" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="O101" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="P101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q101" s="2"/>
+      <c r="R101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF101" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="AG101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH101" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ101" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL101" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AM101" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AN101" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="AO101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP101" t="s" s="2">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="B102" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="C102" s="2"/>
+      <c r="D102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E102" s="2"/>
+      <c r="F102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G102" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K102" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="L102" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="M102" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="O102" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="P102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q102" s="2"/>
+      <c r="R102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X102" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="Z102" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF102" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="AG102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH102" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI102" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AJ102" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM102" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AN102" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="AO102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP102" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="C103" s="2"/>
+      <c r="D103" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="E103" s="2"/>
+      <c r="F103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K103" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="L103" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="M103" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="O103" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="P103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q103" s="2"/>
+      <c r="R103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X103" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="Y103" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="Z103" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AA103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF103" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="AG103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ103" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL103" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AM103" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AN103" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="AO103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP103" t="s" s="2">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="C104" s="2"/>
+      <c r="D104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E104" s="2"/>
+      <c r="F104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K104" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="L104" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="M104" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="O104" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="P104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q104" s="2"/>
+      <c r="R104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF104" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="AG104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ104" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM104" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="AN104" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AO104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP104" t="s" s="2">
         <v>83</v>
       </c>
     </row>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
@@ -2097,15 +2097,15 @@
   <dimension ref="A1:AP104"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="47.2890625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="44.67578125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="14.94140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="40.54296875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="38.30078125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="12.80859375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2116,28 +2116,28 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="111.37890625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="70.58203125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="41.01953125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="95.48828125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="60.51171875" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="35.16796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="247.40625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="212.10546875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="91.75" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="36.3046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
@@ -642,7 +642,7 @@
   </si>
   <si>
     <t>3つのコードを設定する。
-第1コード（first）は、simpleObservationコード体系を必須とし、procedureを設定する。
+第1コード（first）は、simpleObservationコード体系を必須とし、examを設定する。
 第2コード（second）は、歯科を表すコードLP89803-8を設定する。
 第3コード（third）は、歯の有無や処置状態などを表すコードを設定する。なお、日本では適切なコード体系が存在しないため、独自のバリューセットを定義する。</t>
   </si>
@@ -833,7 +833,7 @@
     <t>システム内の特定のコードを参照する必要があります。 / Need to refer to a particular code in the system.</t>
   </si>
   <si>
-    <t>procedure</t>
+    <t>exam</t>
   </si>
   <si>
     <t>Coding.code</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-30</t>
+    <t>2024-06-24</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-24</t>
+    <t>2025-07-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
@@ -383,7 +383,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -629,7 +629,7 @@
     <t>高レベルの観測カテゴリのコード。 / Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">value:coding.system}
@@ -1031,7 +1031,7 @@
     <t>単純な観測の名前を識別するコード。 / Codes identifying names of simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1125,7 +1125,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1301,7 +1301,7 @@
     <t>結果（ `Observation.value[x]`）が欠落している理由を指定するコード。 / Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">obs-6
@@ -1330,7 +1330,7 @@
     <t>観測の解釈を識別するコード。 / Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1560,7 +1560,7 @@
     <t>単純な観測の方法。 / Methods for simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-methods</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-methods|4.0.1</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1597,7 +1597,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
 </t>
   </si>
   <si>
@@ -1672,7 +1672,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1722,7 +1722,7 @@
     <t>参照範囲の意味のコード。 / Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1755,7 +1755,7 @@
     <t>参照範囲が適用される母集団を識別するコード。 / Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
@@ -632,7 +632,7 @@
     <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
-    <t xml:space="preserve">value:coding.system}
+    <t xml:space="preserve">pattern:$this}
 </t>
   </si>
   <si>
@@ -4824,7 +4824,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>94</v>
@@ -6272,7 +6272,7 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>94</v>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>94</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4554" uniqueCount="615">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4554" uniqueCount="616">
   <si>
     <t>Property</t>
   </si>
@@ -919,6 +919,14 @@
     <t>階層的にカテゴリーを設定することで粒度のレベルを概念定義できる。</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://loinc.org"/&gt;
+    &lt;code value="LP89803-8"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>Observation.category:second.id</t>
   </si>
   <si>
@@ -935,9 +943,6 @@
   </si>
   <si>
     <t>Observation.category:second.coding.system</t>
-  </si>
-  <si>
-    <t>http://loinc.org</t>
   </si>
   <si>
     <t>Observation.category:second.coding.version</t>
@@ -1071,6 +1076,9 @@
   </si>
   <si>
     <t>Observation.code.coding.system</t>
+  </si>
+  <si>
+    <t>http://loinc.org</t>
   </si>
   <si>
     <t>Observation.code.coding.version</t>
@@ -5589,7 +5597,7 @@
         <v>83</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>83</v>
+        <v>291</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>83</v>
@@ -5663,7 +5671,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B29" t="s" s="2">
         <v>207</v>
@@ -5781,7 +5789,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>214</v>
@@ -5901,7 +5909,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>220</v>
@@ -6023,7 +6031,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>230</v>
@@ -6141,7 +6149,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>232</v>
@@ -6261,7 +6269,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>234</v>
@@ -6306,7 +6314,7 @@
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>297</v>
+        <v>83</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>83</v>
@@ -9198,7 +9206,7 @@
       </c>
       <c r="Q58" s="2"/>
       <c r="R58" t="s" s="2">
-        <v>297</v>
+        <v>342</v>
       </c>
       <c r="S58" t="s" s="2">
         <v>83</v>
@@ -9275,10 +9283,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9395,10 +9403,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9438,7 +9446,7 @@
       </c>
       <c r="Q60" s="2"/>
       <c r="R60" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="S60" t="s" s="2">
         <v>83</v>
@@ -9515,10 +9523,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9561,7 +9569,7 @@
         <v>83</v>
       </c>
       <c r="S61" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="T61" t="s" s="2">
         <v>83</v>
@@ -9635,10 +9643,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9757,10 +9765,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9879,10 +9887,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9905,19 +9913,19 @@
         <v>95</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
@@ -9966,7 +9974,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9981,19 +9989,19 @@
         <v>106</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>83</v>
@@ -10001,10 +10009,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10027,16 +10035,16 @@
         <v>95</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10086,7 +10094,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10110,10 +10118,10 @@
         <v>331</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>83</v>
@@ -10121,14 +10129,14 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -10147,19 +10155,19 @@
         <v>95</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>83</v>
@@ -10208,7 +10216,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10223,19 +10231,19 @@
         <v>106</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>83</v>
@@ -10243,14 +10251,14 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10269,19 +10277,19 @@
         <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
@@ -10330,7 +10338,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10345,19 +10353,19 @@
         <v>106</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>83</v>
@@ -10365,10 +10373,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10391,16 +10399,16 @@
         <v>95</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10450,7 +10458,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10471,13 +10479,13 @@
         <v>83</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>83</v>
@@ -10485,10 +10493,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10511,19 +10519,19 @@
         <v>95</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>83</v>
@@ -10572,7 +10580,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10587,19 +10595,19 @@
         <v>106</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>83</v>
@@ -10607,10 +10615,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10636,16 +10644,16 @@
         <v>191</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>83</v>
@@ -10674,7 +10682,7 @@
       </c>
       <c r="Y70" s="2"/>
       <c r="Z70" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>83</v>
@@ -10692,7 +10700,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10701,7 +10709,7 @@
         <v>94</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>106</v>
@@ -10710,27 +10718,27 @@
         <v>83</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10756,16 +10764,16 @@
         <v>191</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>83</v>
@@ -10790,13 +10798,13 @@
         <v>83</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>83</v>
@@ -10814,7 +10822,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10823,7 +10831,7 @@
         <v>94</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>106</v>
@@ -10838,7 +10846,7 @@
         <v>137</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>83</v>
@@ -10849,14 +10857,14 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -10878,16 +10886,16 @@
         <v>191</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>83</v>
@@ -10912,13 +10920,13 @@
         <v>83</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>83</v>
@@ -10936,7 +10944,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -10954,27 +10962,27 @@
         <v>83</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10997,19 +11005,19 @@
         <v>83</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>83</v>
@@ -11058,7 +11066,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -11079,10 +11087,10 @@
         <v>83</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>83</v>
@@ -11093,10 +11101,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11122,13 +11130,13 @@
         <v>191</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11158,7 +11166,7 @@
       </c>
       <c r="Y74" s="2"/>
       <c r="Z74" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>83</v>
@@ -11176,7 +11184,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11194,27 +11202,27 @@
         <v>83</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11329,10 +11337,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11449,13 +11457,13 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="B77" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="B77" t="s" s="2">
-        <v>445</v>
-      </c>
       <c r="C77" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D77" t="s" s="2">
         <v>83</v>
@@ -11477,13 +11485,13 @@
         <v>83</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11569,10 +11577,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11687,10 +11695,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11716,10 +11724,10 @@
         <v>140</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11805,10 +11813,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11834,13 +11842,13 @@
         <v>108</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11848,7 +11856,7 @@
       </c>
       <c r="Q80" s="2"/>
       <c r="R80" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="S80" t="s" s="2">
         <v>83</v>
@@ -11890,7 +11898,7 @@
         <v>83</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>94</v>
@@ -11925,10 +11933,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11954,10 +11962,10 @@
         <v>191</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -11988,7 +11996,7 @@
       </c>
       <c r="Y81" s="2"/>
       <c r="Z81" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>83</v>
@@ -12006,7 +12014,7 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -12041,10 +12049,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12159,10 +12167,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12279,10 +12287,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12401,10 +12409,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12519,10 +12527,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12639,10 +12647,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12684,7 +12692,7 @@
       </c>
       <c r="Q87" s="2"/>
       <c r="R87" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="S87" t="s" s="2">
         <v>83</v>
@@ -12761,10 +12769,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12881,10 +12889,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13001,10 +13009,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13121,10 +13129,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13243,10 +13251,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13365,10 +13373,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13487,10 +13495,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13609,10 +13617,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13638,16 +13646,16 @@
         <v>191</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>83</v>
@@ -13675,10 +13683,10 @@
         <v>326</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>83</v>
@@ -13696,7 +13704,7 @@
         <v>83</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -13717,10 +13725,10 @@
         <v>83</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>83</v>
@@ -13731,10 +13739,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13757,16 +13765,16 @@
         <v>83</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -13816,7 +13824,7 @@
         <v>83</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
@@ -13834,27 +13842,27 @@
         <v>83</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13877,16 +13885,16 @@
         <v>83</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -13936,7 +13944,7 @@
         <v>83</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
@@ -13954,27 +13962,27 @@
         <v>83</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP97" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13997,19 +14005,19 @@
         <v>83</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>83</v>
@@ -14058,7 +14066,7 @@
         <v>83</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -14070,7 +14078,7 @@
         <v>83</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>83</v>
@@ -14079,10 +14087,10 @@
         <v>83</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>83</v>
@@ -14093,10 +14101,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14211,10 +14219,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14331,14 +14339,14 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -14360,10 +14368,10 @@
         <v>140</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="N101" t="s" s="2">
         <v>143</v>
@@ -14418,7 +14426,7 @@
         <v>83</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>81</v>
@@ -14453,10 +14461,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14479,13 +14487,13 @@
         <v>83</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -14536,7 +14544,7 @@
         <v>83</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>81</v>
@@ -14545,7 +14553,7 @@
         <v>94</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AJ102" t="s" s="2">
         <v>106</v>
@@ -14557,10 +14565,10 @@
         <v>83</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>83</v>
@@ -14571,10 +14579,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14597,13 +14605,13 @@
         <v>83</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -14654,7 +14662,7 @@
         <v>83</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>81</v>
@@ -14663,7 +14671,7 @@
         <v>94</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>106</v>
@@ -14675,10 +14683,10 @@
         <v>83</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>83</v>
@@ -14689,10 +14697,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14718,16 +14726,16 @@
         <v>191</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>83</v>
@@ -14755,10 +14763,10 @@
         <v>118</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>83</v>
@@ -14776,7 +14784,7 @@
         <v>83</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>81</v>
@@ -14794,13 +14802,13 @@
         <v>83</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>83</v>
@@ -14811,10 +14819,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14840,16 +14848,16 @@
         <v>191</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>83</v>
@@ -14877,10 +14885,10 @@
         <v>326</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>83</v>
@@ -14898,7 +14906,7 @@
         <v>83</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>81</v>
@@ -14916,13 +14924,13 @@
         <v>83</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>83</v>
@@ -14933,10 +14941,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14959,17 +14967,17 @@
         <v>83</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>83</v>
@@ -15018,7 +15026,7 @@
         <v>83</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>81</v>
@@ -15042,7 +15050,7 @@
         <v>83</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>83</v>
@@ -15053,10 +15061,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15082,10 +15090,10 @@
         <v>208</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -15136,7 +15144,7 @@
         <v>83</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>81</v>
@@ -15157,10 +15165,10 @@
         <v>83</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>83</v>
@@ -15171,10 +15179,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15197,16 +15205,16 @@
         <v>95</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -15256,7 +15264,7 @@
         <v>83</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>81</v>
@@ -15277,10 +15285,10 @@
         <v>83</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>83</v>
@@ -15291,10 +15299,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15317,16 +15325,16 @@
         <v>95</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -15376,7 +15384,7 @@
         <v>83</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>81</v>
@@ -15397,10 +15405,10 @@
         <v>83</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>83</v>
@@ -15411,10 +15419,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15437,19 +15445,19 @@
         <v>95</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>83</v>
@@ -15498,7 +15506,7 @@
         <v>83</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>81</v>
@@ -15519,10 +15527,10 @@
         <v>83</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>83</v>
@@ -15533,10 +15541,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15651,10 +15659,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15771,14 +15779,14 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
@@ -15800,10 +15808,10 @@
         <v>140</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="N113" t="s" s="2">
         <v>143</v>
@@ -15858,7 +15866,7 @@
         <v>83</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>81</v>
@@ -15893,10 +15901,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15922,13 +15930,13 @@
         <v>191</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="O114" t="s" s="2">
         <v>325</v>
@@ -15980,7 +15988,7 @@
         <v>83</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>94</v>
@@ -15998,7 +16006,7 @@
         <v>83</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AM114" t="s" s="2">
         <v>331</v>
@@ -16015,10 +16023,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16041,19 +16049,19 @@
         <v>95</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>83</v>
@@ -16102,7 +16110,7 @@
         <v>83</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>81</v>
@@ -16120,27 +16128,27 @@
         <v>83</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP115" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16166,16 +16174,16 @@
         <v>191</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>83</v>
@@ -16200,13 +16208,13 @@
         <v>83</v>
       </c>
       <c r="X116" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Y116" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Z116" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>83</v>
@@ -16224,7 +16232,7 @@
         <v>83</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>81</v>
@@ -16233,7 +16241,7 @@
         <v>94</v>
       </c>
       <c r="AI116" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AJ116" t="s" s="2">
         <v>106</v>
@@ -16248,7 +16256,7 @@
         <v>137</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>83</v>
@@ -16259,14 +16267,14 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
@@ -16288,16 +16296,16 @@
         <v>191</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>83</v>
@@ -16322,13 +16330,13 @@
         <v>83</v>
       </c>
       <c r="X117" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Y117" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="Z117" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>83</v>
@@ -16346,7 +16354,7 @@
         <v>83</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>81</v>
@@ -16364,27 +16372,27 @@
         <v>83</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AO117" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP117" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16410,16 +16418,16 @@
         <v>84</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="O118" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>83</v>
@@ -16468,7 +16476,7 @@
         <v>83</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>81</v>
@@ -16489,10 +16497,10 @@
         <v>83</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AO118" t="s" s="2">
         <v>83</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
@@ -1112,7 +1112,7 @@
     <t>観察対象者 【JP Core仕様】患者情報</t>
   </si>
   <si>
-    <t>この要素は1..1のcardinalityになるはずと考えられる。この要素が欠損値になる唯一の状況は、対象患者が不明なデバイスによって観察が行われるケースである。この場合、観察は何らかのコンテキスト/チャネルマッチング技術を介して患者にマッチングされる必要があり、患者にマッチングされれば、その時点で本要素を更新する必要がある。</t>
+    <t>この要素は1..1のcardinalityになるはずと考えられる。この要素が欠損値になる唯一の状況は、対象患者が不明な機器によって観察が行われるケースである。この場合、観察は何らかのコンテキスト・チャネル照合技術を介して患者に照合される必要があり、患者に照合されれば、その時点で本要素を更新する必要がある。</t>
   </si>
   <si>
     <t>あなたが彼らが誰または何をしているのかわからない場合、観察には価値がありません。 / Observations have no value if you don't know who or what they're about.</t>
@@ -1157,7 +1157,7 @@
 </t>
   </si>
   <si>
-    <t>このobservationが行われるヘルスケアイベント</t>
+    <t>このobservationが行われる診療イベント</t>
   </si>
   <si>
     <t>例：診療、歯科検診、身元不明者調査</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4554" uniqueCount="616">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4554" uniqueCount="614">
   <si>
     <t>Property</t>
   </si>
@@ -657,6 +657,14 @@
     <t>必要なカテゴリバリューセットに加えて、この要素は、所有者のカテゴリの定義に基づいてさまざまな分類スキームを許可し、効果的に複数のカテゴリを一度に使用できます。粒度のレベルは、値セットのカテゴリの概念によって定義されます。 / In addition to the required category valueset, this element allows various categorization schemes based on the owner’s definition of the category and effectively multiple categories can be used at once.  The level of granularity is defined by the category concepts in the value set.</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://jpfhir.jp/fhir/core/CodeSystem/JP_SimpleObservationCategory_CS"/&gt;
+    &lt;code value="exam"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS</t>
   </si>
   <si>
@@ -811,9 +819,6 @@
   </si>
   <si>
     <t>システム内の特定のコードを参照する必要があります。 / Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>exam</t>
   </si>
   <si>
     <t>Coding.code</t>
@@ -951,9 +956,6 @@
     <t>Observation.category:second.coding.code</t>
   </si>
   <si>
-    <t>LP89803-8</t>
-  </si>
-  <si>
     <t>Observation.category:second.coding.display</t>
   </si>
   <si>
@@ -972,6 +974,14 @@
     <t>このObservationに関する詳細分類、JP_ObservationDetailedDentalCategory_VSより選択する、必須項目</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://jpfhir.jp/fhir/core/CodeSystem/JP_ObservationDentalCategory_CS"/&gt;
+    &lt;code value="DO-1-01"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationDetailedDentalCategory_VS</t>
   </si>
   <si>
@@ -993,16 +1003,10 @@
     <t>Observation.category:third.coding.system</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_ObservationDentalCategory_CS</t>
-  </si>
-  <si>
     <t>Observation.category:third.coding.version</t>
   </si>
   <si>
     <t>Observation.category:third.coding.code</t>
-  </si>
-  <si>
-    <t>DO-1-01</t>
   </si>
   <si>
     <t>Observation.category:third.coding.display</t>
@@ -4151,7 +4155,7 @@
         <v>83</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>83</v>
+        <v>205</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>83</v>
@@ -4170,7 +4174,7 @@
       </c>
       <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>83</v>
@@ -4223,10 +4227,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4249,13 +4253,13 @@
         <v>83</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4306,7 +4310,7 @@
         <v>83</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -4330,7 +4334,7 @@
         <v>83</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>83</v>
@@ -4341,10 +4345,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4373,7 +4377,7 @@
         <v>141</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>143</v>
@@ -4414,10 +4418,10 @@
         <v>83</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>83</v>
@@ -4426,7 +4430,7 @@
         <v>198</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4450,7 +4454,7 @@
         <v>83</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>83</v>
@@ -4461,10 +4465,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4487,19 +4491,19 @@
         <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>83</v>
@@ -4548,7 +4552,7 @@
         <v>83</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4569,10 +4573,10 @@
         <v>83</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>83</v>
@@ -4583,10 +4587,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4609,13 +4613,13 @@
         <v>83</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4666,7 +4670,7 @@
         <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4690,7 +4694,7 @@
         <v>83</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>83</v>
@@ -4701,10 +4705,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4733,7 +4737,7 @@
         <v>141</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>143</v>
@@ -4774,10 +4778,10 @@
         <v>83</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>83</v>
@@ -4786,7 +4790,7 @@
         <v>198</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4810,7 +4814,7 @@
         <v>83</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>83</v>
@@ -4821,10 +4825,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4850,23 +4854,23 @@
         <v>108</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="S22" t="s" s="2">
         <v>83</v>
@@ -4908,7 +4912,7 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -4929,10 +4933,10 @@
         <v>83</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>83</v>
@@ -4943,10 +4947,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4969,16 +4973,16 @@
         <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -5028,7 +5032,7 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -5049,10 +5053,10 @@
         <v>83</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>83</v>
@@ -5063,10 +5067,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5092,21 +5096,21 @@
         <v>114</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>256</v>
+        <v>83</v>
       </c>
       <c r="S24" t="s" s="2">
         <v>83</v>
@@ -5209,7 +5213,7 @@
         <v>95</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>262</v>
@@ -5451,7 +5455,7 @@
         <v>95</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L27" t="s" s="2">
         <v>280</v>
@@ -5674,7 +5678,7 @@
         <v>292</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5697,13 +5701,13 @@
         <v>83</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5754,7 +5758,7 @@
         <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5778,7 +5782,7 @@
         <v>83</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>83</v>
@@ -5792,7 +5796,7 @@
         <v>293</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5821,7 +5825,7 @@
         <v>141</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N30" t="s" s="2">
         <v>143</v>
@@ -5862,10 +5866,10 @@
         <v>83</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>83</v>
@@ -5874,7 +5878,7 @@
         <v>198</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5898,7 +5902,7 @@
         <v>83</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>83</v>
@@ -5912,7 +5916,7 @@
         <v>294</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5935,19 +5939,19 @@
         <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>83</v>
@@ -5996,7 +6000,7 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -6017,10 +6021,10 @@
         <v>83</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>83</v>
@@ -6034,7 +6038,7 @@
         <v>295</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6057,13 +6061,13 @@
         <v>83</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6114,7 +6118,7 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -6138,7 +6142,7 @@
         <v>83</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>83</v>
@@ -6152,7 +6156,7 @@
         <v>296</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6181,7 +6185,7 @@
         <v>141</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N33" t="s" s="2">
         <v>143</v>
@@ -6222,10 +6226,10 @@
         <v>83</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>83</v>
@@ -6234,7 +6238,7 @@
         <v>198</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -6258,7 +6262,7 @@
         <v>83</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>83</v>
@@ -6272,7 +6276,7 @@
         <v>297</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6298,16 +6302,16 @@
         <v>108</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>83</v>
@@ -6356,7 +6360,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6377,10 +6381,10 @@
         <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>83</v>
@@ -6394,7 +6398,7 @@
         <v>298</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6417,16 +6421,16 @@
         <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6476,7 +6480,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6497,10 +6501,10 @@
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>83</v>
@@ -6514,7 +6518,7 @@
         <v>299</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6540,21 +6544,21 @@
         <v>114</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>300</v>
+        <v>83</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>83</v>
@@ -6631,7 +6635,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>261</v>
@@ -6657,7 +6661,7 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L37" t="s" s="2">
         <v>262</v>
@@ -6751,7 +6755,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>269</v>
@@ -6873,7 +6877,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>279</v>
@@ -6899,7 +6903,7 @@
         <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L39" t="s" s="2">
         <v>280</v>
@@ -6995,13 +6999,13 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>189</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D40" t="s" s="2">
         <v>83</v>
@@ -7026,10 +7030,10 @@
         <v>191</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="N40" t="s" s="2">
         <v>290</v>
@@ -7045,7 +7049,7 @@
         <v>83</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>83</v>
+        <v>306</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>83</v>
@@ -7120,7 +7124,7 @@
         <v>308</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7143,13 +7147,13 @@
         <v>83</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7200,7 +7204,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -7224,7 +7228,7 @@
         <v>83</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>83</v>
@@ -7238,7 +7242,7 @@
         <v>309</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7267,7 +7271,7 @@
         <v>141</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N42" t="s" s="2">
         <v>143</v>
@@ -7308,10 +7312,10 @@
         <v>83</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>83</v>
@@ -7320,7 +7324,7 @@
         <v>198</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7344,7 +7348,7 @@
         <v>83</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>83</v>
@@ -7358,7 +7362,7 @@
         <v>310</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7381,19 +7385,19 @@
         <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>83</v>
@@ -7442,7 +7446,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7463,10 +7467,10 @@
         <v>83</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>83</v>
@@ -7480,7 +7484,7 @@
         <v>311</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7503,13 +7507,13 @@
         <v>83</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7560,7 +7564,7 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7584,7 +7588,7 @@
         <v>83</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>83</v>
@@ -7598,7 +7602,7 @@
         <v>312</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7627,7 +7631,7 @@
         <v>141</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>143</v>
@@ -7668,10 +7672,10 @@
         <v>83</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>83</v>
@@ -7680,7 +7684,7 @@
         <v>198</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7704,7 +7708,7 @@
         <v>83</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>83</v>
@@ -7718,7 +7722,7 @@
         <v>313</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7744,23 +7748,23 @@
         <v>108</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
-        <v>314</v>
+        <v>83</v>
       </c>
       <c r="S46" t="s" s="2">
         <v>83</v>
@@ -7802,7 +7806,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7823,10 +7827,10 @@
         <v>83</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>83</v>
@@ -7837,10 +7841,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7863,16 +7867,16 @@
         <v>95</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7922,7 +7926,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7943,10 +7947,10 @@
         <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>83</v>
@@ -7957,10 +7961,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7986,21 +7990,21 @@
         <v>114</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
-        <v>317</v>
+        <v>83</v>
       </c>
       <c r="S48" t="s" s="2">
         <v>83</v>
@@ -8077,7 +8081,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B49" t="s" s="2">
         <v>261</v>
@@ -8103,7 +8107,7 @@
         <v>95</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L49" t="s" s="2">
         <v>262</v>
@@ -8197,7 +8201,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B50" t="s" s="2">
         <v>269</v>
@@ -8319,7 +8323,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>279</v>
@@ -8345,7 +8349,7 @@
         <v>95</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L51" t="s" s="2">
         <v>280</v>
@@ -8441,14 +8445,14 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8470,16 +8474,16 @@
         <v>191</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="O52" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8504,14 +8508,14 @@
         <v>83</v>
       </c>
       <c r="X52" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="Z52" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="Y52" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>328</v>
-      </c>
       <c r="AA52" t="s" s="2">
         <v>83</v>
       </c>
@@ -8528,7 +8532,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>94</v>
@@ -8543,30 +8547,30 @@
         <v>106</v>
       </c>
       <c r="AK52" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AM52" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="AL52" t="s" s="2">
+      <c r="AN52" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="AM52" t="s" s="2">
+      <c r="AO52" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="AN52" t="s" s="2">
+      <c r="AP52" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="AO52" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="AP52" t="s" s="2">
-        <v>334</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8589,13 +8593,13 @@
         <v>83</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8646,7 +8650,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8670,7 +8674,7 @@
         <v>83</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>83</v>
@@ -8681,10 +8685,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8713,7 +8717,7 @@
         <v>141</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>143</v>
@@ -8754,10 +8758,10 @@
         <v>83</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>83</v>
@@ -8766,7 +8770,7 @@
         <v>198</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8790,7 +8794,7 @@
         <v>83</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>83</v>
@@ -8801,10 +8805,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8827,19 +8831,19 @@
         <v>95</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>83</v>
@@ -8888,7 +8892,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8909,10 +8913,10 @@
         <v>83</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>83</v>
@@ -8923,10 +8927,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8949,13 +8953,13 @@
         <v>83</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9006,7 +9010,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -9030,7 +9034,7 @@
         <v>83</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>83</v>
@@ -9041,10 +9045,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9073,7 +9077,7 @@
         <v>141</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>143</v>
@@ -9114,10 +9118,10 @@
         <v>83</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD57" t="s" s="2">
         <v>83</v>
@@ -9126,7 +9130,7 @@
         <v>198</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9150,7 +9154,7 @@
         <v>83</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>83</v>
@@ -9161,10 +9165,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9190,23 +9194,23 @@
         <v>108</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q58" s="2"/>
       <c r="R58" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="S58" t="s" s="2">
         <v>83</v>
@@ -9248,7 +9252,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9269,10 +9273,10 @@
         <v>83</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>83</v>
@@ -9283,10 +9287,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9309,16 +9313,16 @@
         <v>95</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9368,7 +9372,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9389,10 +9393,10 @@
         <v>83</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
@@ -9403,10 +9407,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9432,21 +9436,21 @@
         <v>114</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q60" s="2"/>
       <c r="R60" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="S60" t="s" s="2">
         <v>83</v>
@@ -9523,10 +9527,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9549,7 +9553,7 @@
         <v>95</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L61" t="s" s="2">
         <v>262</v>
@@ -9569,7 +9573,7 @@
         <v>83</v>
       </c>
       <c r="S61" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="T61" t="s" s="2">
         <v>83</v>
@@ -9643,10 +9647,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9765,10 +9769,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9791,7 +9795,7 @@
         <v>95</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L63" t="s" s="2">
         <v>280</v>
@@ -9887,10 +9891,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9913,19 +9917,19 @@
         <v>95</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="N64" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="L64" t="s" s="2">
+      <c r="O64" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>354</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
@@ -9974,7 +9978,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9989,19 +9993,19 @@
         <v>106</v>
       </c>
       <c r="AK64" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AN64" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="AL64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM64" t="s" s="2">
+      <c r="AO64" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>83</v>
@@ -10009,10 +10013,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10035,16 +10039,16 @@
         <v>95</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="N65" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="L65" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10094,7 +10098,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10115,13 +10119,13 @@
         <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>83</v>
@@ -10129,14 +10133,14 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -10155,19 +10159,19 @@
         <v>95</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="N66" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="L66" t="s" s="2">
+      <c r="O66" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>369</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>83</v>
@@ -10216,7 +10220,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10231,19 +10235,19 @@
         <v>106</v>
       </c>
       <c r="AK66" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="AN66" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="AL66" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM66" t="s" s="2">
+      <c r="AO66" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="AO66" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>83</v>
@@ -10251,14 +10255,14 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10277,19 +10281,19 @@
         <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="N67" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="L67" t="s" s="2">
+      <c r="O67" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
@@ -10338,7 +10342,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10353,19 +10357,19 @@
         <v>106</v>
       </c>
       <c r="AK67" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AN67" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="AL67" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM67" t="s" s="2">
+      <c r="AO67" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="AO67" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>83</v>
@@ -10373,10 +10377,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10399,16 +10403,16 @@
         <v>95</v>
       </c>
       <c r="K68" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="N68" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="L68" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>387</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10458,7 +10462,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10479,13 +10483,13 @@
         <v>83</v>
       </c>
       <c r="AM68" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AO68" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="AO68" t="s" s="2">
-        <v>390</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>83</v>
@@ -10493,10 +10497,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10519,19 +10523,19 @@
         <v>95</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="N69" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="L69" t="s" s="2">
+      <c r="O69" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>83</v>
@@ -10580,7 +10584,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10595,19 +10599,19 @@
         <v>106</v>
       </c>
       <c r="AK69" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AN69" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="AL69" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM69" t="s" s="2">
+      <c r="AO69" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="AO69" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>83</v>
@@ -10615,10 +10619,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10644,16 +10648,16 @@
         <v>191</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="O70" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>403</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>83</v>
@@ -10682,7 +10686,7 @@
       </c>
       <c r="Y70" s="2"/>
       <c r="Z70" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>83</v>
@@ -10700,7 +10704,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10709,7 +10713,7 @@
         <v>94</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>106</v>
@@ -10718,27 +10722,27 @@
         <v>83</v>
       </c>
       <c r="AL70" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AN70" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="AM70" t="s" s="2">
+      <c r="AO70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP70" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="AO70" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP70" t="s" s="2">
-        <v>409</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10764,16 +10768,16 @@
         <v>191</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="O71" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>83</v>
@@ -10798,14 +10802,14 @@
         <v>83</v>
       </c>
       <c r="X71" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="Z71" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="Y71" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="Z71" t="s" s="2">
-        <v>416</v>
-      </c>
       <c r="AA71" t="s" s="2">
         <v>83</v>
       </c>
@@ -10822,7 +10826,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10831,7 +10835,7 @@
         <v>94</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>106</v>
@@ -10846,7 +10850,7 @@
         <v>137</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>83</v>
@@ -10857,14 +10861,14 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -10886,16 +10890,16 @@
         <v>191</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="O72" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>83</v>
@@ -10920,13 +10924,13 @@
         <v>83</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>83</v>
@@ -10944,7 +10948,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -10962,27 +10966,27 @@
         <v>83</v>
       </c>
       <c r="AL72" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AN72" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="AM72" t="s" s="2">
+      <c r="AO72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP72" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="AO72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP72" t="s" s="2">
-        <v>429</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11005,19 +11009,19 @@
         <v>83</v>
       </c>
       <c r="K73" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="N73" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="L73" t="s" s="2">
+      <c r="O73" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>434</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>83</v>
@@ -11066,7 +11070,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -11087,10 +11091,10 @@
         <v>83</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>83</v>
@@ -11101,10 +11105,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11130,13 +11134,13 @@
         <v>191</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11166,7 +11170,7 @@
       </c>
       <c r="Y74" s="2"/>
       <c r="Z74" t="s" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>83</v>
@@ -11184,7 +11188,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11202,27 +11206,27 @@
         <v>83</v>
       </c>
       <c r="AL74" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="AN74" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="AM74" t="s" s="2">
+      <c r="AO74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP74" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="AO74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP74" t="s" s="2">
-        <v>444</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11245,13 +11249,13 @@
         <v>83</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11302,7 +11306,7 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11326,7 +11330,7 @@
         <v>83</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>83</v>
@@ -11337,10 +11341,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11369,7 +11373,7 @@
         <v>141</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N76" t="s" s="2">
         <v>143</v>
@@ -11410,10 +11414,10 @@
         <v>83</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC76" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD76" t="s" s="2">
         <v>83</v>
@@ -11422,7 +11426,7 @@
         <v>198</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11446,7 +11450,7 @@
         <v>83</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>83</v>
@@ -11457,13 +11461,13 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B77" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="C77" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="C77" t="s" s="2">
-        <v>448</v>
       </c>
       <c r="D77" t="s" s="2">
         <v>83</v>
@@ -11485,13 +11489,13 @@
         <v>83</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11542,7 +11546,7 @@
         <v>83</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11577,10 +11581,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11603,13 +11607,13 @@
         <v>83</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11660,7 +11664,7 @@
         <v>83</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11684,7 +11688,7 @@
         <v>83</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>83</v>
@@ -11695,10 +11699,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11724,10 +11728,10 @@
         <v>140</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11766,10 +11770,10 @@
         <v>83</v>
       </c>
       <c r="AB79" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC79" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD79" t="s" s="2">
         <v>83</v>
@@ -11778,7 +11782,7 @@
         <v>198</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -11813,10 +11817,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11842,13 +11846,13 @@
         <v>108</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="N80" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11856,7 +11860,7 @@
       </c>
       <c r="Q80" s="2"/>
       <c r="R80" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="S80" t="s" s="2">
         <v>83</v>
@@ -11898,7 +11902,7 @@
         <v>83</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>94</v>
@@ -11933,10 +11937,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11962,10 +11966,10 @@
         <v>191</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -11996,7 +12000,7 @@
       </c>
       <c r="Y81" s="2"/>
       <c r="Z81" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>83</v>
@@ -12014,7 +12018,7 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -12049,10 +12053,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12075,13 +12079,13 @@
         <v>83</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -12132,7 +12136,7 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -12156,7 +12160,7 @@
         <v>83</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>83</v>
@@ -12167,10 +12171,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12199,7 +12203,7 @@
         <v>141</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N83" t="s" s="2">
         <v>143</v>
@@ -12240,10 +12244,10 @@
         <v>83</v>
       </c>
       <c r="AB83" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC83" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD83" t="s" s="2">
         <v>83</v>
@@ -12252,7 +12256,7 @@
         <v>198</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12276,7 +12280,7 @@
         <v>83</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>83</v>
@@ -12287,10 +12291,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12313,19 +12317,19 @@
         <v>95</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>83</v>
@@ -12374,7 +12378,7 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12395,10 +12399,10 @@
         <v>83</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>83</v>
@@ -12409,10 +12413,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12435,13 +12439,13 @@
         <v>83</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12492,7 +12496,7 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12516,7 +12520,7 @@
         <v>83</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>83</v>
@@ -12527,10 +12531,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12559,7 +12563,7 @@
         <v>141</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N86" t="s" s="2">
         <v>143</v>
@@ -12600,10 +12604,10 @@
         <v>83</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC86" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD86" t="s" s="2">
         <v>83</v>
@@ -12612,7 +12616,7 @@
         <v>198</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -12636,7 +12640,7 @@
         <v>83</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>83</v>
@@ -12647,10 +12651,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12676,23 +12680,23 @@
         <v>108</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q87" s="2"/>
       <c r="R87" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="S87" t="s" s="2">
         <v>83</v>
@@ -12734,7 +12738,7 @@
         <v>83</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -12755,10 +12759,10 @@
         <v>83</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>83</v>
@@ -12769,10 +12773,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12795,16 +12799,16 @@
         <v>95</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -12854,7 +12858,7 @@
         <v>83</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -12875,10 +12879,10 @@
         <v>83</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>83</v>
@@ -12889,10 +12893,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12918,14 +12922,14 @@
         <v>114</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>83</v>
@@ -13009,10 +13013,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13035,7 +13039,7 @@
         <v>95</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L90" t="s" s="2">
         <v>262</v>
@@ -13129,10 +13133,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13251,10 +13255,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13277,7 +13281,7 @@
         <v>95</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L92" t="s" s="2">
         <v>280</v>
@@ -13373,10 +13377,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13399,19 +13403,19 @@
         <v>95</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>83</v>
@@ -13460,7 +13464,7 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -13481,10 +13485,10 @@
         <v>83</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>83</v>
@@ -13495,10 +13499,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13521,7 +13525,7 @@
         <v>95</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L94" t="s" s="2">
         <v>280</v>
@@ -13617,10 +13621,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13646,16 +13650,16 @@
         <v>191</v>
       </c>
       <c r="L95" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="M95" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="O95" t="s" s="2">
         <v>496</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="O95" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>83</v>
@@ -13680,13 +13684,13 @@
         <v>83</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>83</v>
@@ -13704,7 +13708,7 @@
         <v>83</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -13725,10 +13729,10 @@
         <v>83</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>83</v>
@@ -13739,10 +13743,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13765,16 +13769,16 @@
         <v>83</v>
       </c>
       <c r="K96" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="L96" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="N96" t="s" s="2">
         <v>504</v>
-      </c>
-      <c r="L96" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>506</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -13824,7 +13828,7 @@
         <v>83</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
@@ -13842,27 +13846,27 @@
         <v>83</v>
       </c>
       <c r="AL96" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="AM96" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="AN96" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="AM96" t="s" s="2">
+      <c r="AO96" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP96" t="s" s="2">
         <v>508</v>
-      </c>
-      <c r="AN96" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="AO96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP96" t="s" s="2">
-        <v>510</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13885,16 +13889,16 @@
         <v>83</v>
       </c>
       <c r="K97" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="N97" t="s" s="2">
         <v>512</v>
-      </c>
-      <c r="L97" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>514</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -13944,7 +13948,7 @@
         <v>83</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
@@ -13962,27 +13966,27 @@
         <v>83</v>
       </c>
       <c r="AL97" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="AN97" t="s" s="2">
         <v>515</v>
       </c>
-      <c r="AM97" t="s" s="2">
+      <c r="AO97" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP97" t="s" s="2">
         <v>516</v>
-      </c>
-      <c r="AN97" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="AO97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP97" t="s" s="2">
-        <v>518</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14005,19 +14009,19 @@
         <v>83</v>
       </c>
       <c r="K98" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="L98" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="M98" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="N98" t="s" s="2">
         <v>520</v>
       </c>
-      <c r="L98" t="s" s="2">
+      <c r="O98" t="s" s="2">
         <v>521</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>523</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>83</v>
@@ -14066,7 +14070,7 @@
         <v>83</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -14078,19 +14082,19 @@
         <v>83</v>
       </c>
       <c r="AJ98" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="AK98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM98" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="AN98" t="s" s="2">
         <v>524</v>
-      </c>
-      <c r="AK98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM98" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="AN98" t="s" s="2">
-        <v>526</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>83</v>
@@ -14101,10 +14105,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14127,13 +14131,13 @@
         <v>83</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -14184,7 +14188,7 @@
         <v>83</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>81</v>
@@ -14208,7 +14212,7 @@
         <v>83</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>83</v>
@@ -14219,10 +14223,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14251,7 +14255,7 @@
         <v>141</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N100" t="s" s="2">
         <v>143</v>
@@ -14304,7 +14308,7 @@
         <v>83</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>81</v>
@@ -14328,7 +14332,7 @@
         <v>83</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>83</v>
@@ -14339,14 +14343,14 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -14368,10 +14372,10 @@
         <v>140</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="N101" t="s" s="2">
         <v>143</v>
@@ -14426,7 +14430,7 @@
         <v>83</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>81</v>
@@ -14461,10 +14465,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14487,13 +14491,13 @@
         <v>83</v>
       </c>
       <c r="K102" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="L102" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="M102" t="s" s="2">
         <v>535</v>
-      </c>
-      <c r="L102" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="M102" t="s" s="2">
-        <v>537</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -14544,7 +14548,7 @@
         <v>83</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>81</v>
@@ -14553,7 +14557,7 @@
         <v>94</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="AJ102" t="s" s="2">
         <v>106</v>
@@ -14565,10 +14569,10 @@
         <v>83</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>83</v>
@@ -14579,10 +14583,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14605,13 +14609,13 @@
         <v>83</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -14662,7 +14666,7 @@
         <v>83</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>81</v>
@@ -14671,7 +14675,7 @@
         <v>94</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>106</v>
@@ -14683,10 +14687,10 @@
         <v>83</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>83</v>
@@ -14697,10 +14701,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14726,16 +14730,16 @@
         <v>191</v>
       </c>
       <c r="L104" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="M104" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="N104" t="s" s="2">
         <v>546</v>
       </c>
-      <c r="M104" t="s" s="2">
+      <c r="O104" t="s" s="2">
         <v>547</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="O104" t="s" s="2">
-        <v>549</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>83</v>
@@ -14763,10 +14767,10 @@
         <v>118</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>83</v>
@@ -14784,7 +14788,7 @@
         <v>83</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>81</v>
@@ -14802,13 +14806,13 @@
         <v>83</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>83</v>
@@ -14819,10 +14823,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14848,16 +14852,16 @@
         <v>191</v>
       </c>
       <c r="L105" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="M105" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="N105" t="s" s="2">
         <v>555</v>
       </c>
-      <c r="M105" t="s" s="2">
+      <c r="O105" t="s" s="2">
         <v>556</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="O105" t="s" s="2">
-        <v>558</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>83</v>
@@ -14882,13 +14886,13 @@
         <v>83</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>83</v>
@@ -14906,7 +14910,7 @@
         <v>83</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>81</v>
@@ -14924,13 +14928,13 @@
         <v>83</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>83</v>
@@ -14941,10 +14945,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14967,17 +14971,17 @@
         <v>83</v>
       </c>
       <c r="K106" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="L106" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="M106" t="s" s="2">
         <v>562</v>
-      </c>
-      <c r="L106" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>564</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" t="s" s="2">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>83</v>
@@ -15026,7 +15030,7 @@
         <v>83</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>81</v>
@@ -15050,7 +15054,7 @@
         <v>83</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>83</v>
@@ -15061,10 +15065,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15087,13 +15091,13 @@
         <v>83</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -15144,7 +15148,7 @@
         <v>83</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>81</v>
@@ -15165,10 +15169,10 @@
         <v>83</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>83</v>
@@ -15179,10 +15183,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15205,16 +15209,16 @@
         <v>95</v>
       </c>
       <c r="K108" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="L108" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="M108" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="N108" t="s" s="2">
         <v>572</v>
-      </c>
-      <c r="L108" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="M108" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>574</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -15264,7 +15268,7 @@
         <v>83</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>81</v>
@@ -15285,10 +15289,10 @@
         <v>83</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>83</v>
@@ -15299,10 +15303,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15325,16 +15329,16 @@
         <v>95</v>
       </c>
       <c r="K109" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="L109" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="M109" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="N109" t="s" s="2">
         <v>578</v>
-      </c>
-      <c r="L109" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="M109" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>580</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -15384,7 +15388,7 @@
         <v>83</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>81</v>
@@ -15405,10 +15409,10 @@
         <v>83</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>83</v>
@@ -15419,10 +15423,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15445,19 +15449,19 @@
         <v>95</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="L110" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="M110" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="N110" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="O110" t="s" s="2">
         <v>583</v>
-      </c>
-      <c r="M110" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="O110" t="s" s="2">
-        <v>585</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>83</v>
@@ -15506,7 +15510,7 @@
         <v>83</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>81</v>
@@ -15527,10 +15531,10 @@
         <v>83</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>83</v>
@@ -15541,10 +15545,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15567,13 +15571,13 @@
         <v>83</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -15624,7 +15628,7 @@
         <v>83</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>81</v>
@@ -15648,7 +15652,7 @@
         <v>83</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>83</v>
@@ -15659,10 +15663,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15691,7 +15695,7 @@
         <v>141</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N112" t="s" s="2">
         <v>143</v>
@@ -15744,7 +15748,7 @@
         <v>83</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>81</v>
@@ -15768,7 +15772,7 @@
         <v>83</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>83</v>
@@ -15779,14 +15783,14 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
@@ -15808,10 +15812,10 @@
         <v>140</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="N113" t="s" s="2">
         <v>143</v>
@@ -15866,7 +15870,7 @@
         <v>83</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>81</v>
@@ -15901,10 +15905,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15930,16 +15934,16 @@
         <v>191</v>
       </c>
       <c r="L114" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="M114" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="N114" t="s" s="2">
         <v>592</v>
       </c>
-      <c r="M114" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>594</v>
-      </c>
       <c r="O114" t="s" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>83</v>
@@ -15964,14 +15968,14 @@
         <v>83</v>
       </c>
       <c r="X114" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="Y114" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="Z114" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="Y114" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="Z114" t="s" s="2">
-        <v>328</v>
-      </c>
       <c r="AA114" t="s" s="2">
         <v>83</v>
       </c>
@@ -15988,7 +15992,7 @@
         <v>83</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>94</v>
@@ -16006,16 +16010,16 @@
         <v>83</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="AM114" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="AN114" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AO114" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="AN114" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="AO114" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="AP114" t="s" s="2">
         <v>83</v>
@@ -16023,10 +16027,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16049,19 +16053,19 @@
         <v>95</v>
       </c>
       <c r="K115" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="L115" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="M115" t="s" s="2">
         <v>597</v>
       </c>
-      <c r="L115" t="s" s="2">
+      <c r="N115" t="s" s="2">
         <v>598</v>
       </c>
-      <c r="M115" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="N115" t="s" s="2">
-        <v>600</v>
-      </c>
       <c r="O115" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>83</v>
@@ -16110,7 +16114,7 @@
         <v>83</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>81</v>
@@ -16128,27 +16132,27 @@
         <v>83</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="AM115" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AN115" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AO115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP115" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="AN115" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="AO115" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP115" t="s" s="2">
-        <v>409</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16174,16 +16178,16 @@
         <v>191</v>
       </c>
       <c r="L116" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="M116" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="N116" t="s" s="2">
         <v>603</v>
       </c>
-      <c r="M116" t="s" s="2">
-        <v>604</v>
-      </c>
-      <c r="N116" t="s" s="2">
-        <v>605</v>
-      </c>
       <c r="O116" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>83</v>
@@ -16208,14 +16212,14 @@
         <v>83</v>
       </c>
       <c r="X116" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="Y116" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="Z116" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="Y116" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="Z116" t="s" s="2">
-        <v>416</v>
-      </c>
       <c r="AA116" t="s" s="2">
         <v>83</v>
       </c>
@@ -16232,7 +16236,7 @@
         <v>83</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>81</v>
@@ -16241,7 +16245,7 @@
         <v>94</v>
       </c>
       <c r="AI116" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="AJ116" t="s" s="2">
         <v>106</v>
@@ -16256,7 +16260,7 @@
         <v>137</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>83</v>
@@ -16267,14 +16271,14 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
@@ -16296,16 +16300,16 @@
         <v>191</v>
       </c>
       <c r="L117" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="M117" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="N117" t="s" s="2">
         <v>607</v>
       </c>
-      <c r="M117" t="s" s="2">
+      <c r="O117" t="s" s="2">
         <v>608</v>
-      </c>
-      <c r="N117" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="O117" t="s" s="2">
-        <v>610</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>83</v>
@@ -16330,13 +16334,13 @@
         <v>83</v>
       </c>
       <c r="X117" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="Y117" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="Z117" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>83</v>
@@ -16354,7 +16358,7 @@
         <v>83</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>81</v>
@@ -16372,27 +16376,27 @@
         <v>83</v>
       </c>
       <c r="AL117" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AM117" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AN117" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="AM117" t="s" s="2">
+      <c r="AO117" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP117" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="AN117" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="AO117" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP117" t="s" s="2">
-        <v>429</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16418,16 +16422,16 @@
         <v>84</v>
       </c>
       <c r="L118" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="M118" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="N118" t="s" s="2">
         <v>612</v>
       </c>
-      <c r="M118" t="s" s="2">
+      <c r="O118" t="s" s="2">
         <v>613</v>
-      </c>
-      <c r="N118" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="O118" t="s" s="2">
-        <v>615</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>83</v>
@@ -16476,7 +16480,7 @@
         <v>83</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>81</v>
@@ -16497,10 +16501,10 @@
         <v>83</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="AO118" t="s" s="2">
         <v>83</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
@@ -549,7 +549,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration_Injection|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationDispenseBase|MedicationStatement|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Immunization|ImagingStudy)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration_Injection|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationDispenseBase|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationStatement|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationStatement_Injection|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Immunization|ImagingStudy)
 </t>
   </si>
   <si>
@@ -1116,7 +1116,7 @@
     <t>観察対象者 【JP Core仕様】患者情報</t>
   </si>
   <si>
-    <t>この要素は1..1のcardinalityになるはずと考えられる。この要素が欠損値になる唯一の状況は、対象患者が不明な機器によって観察が行われるケースである。この場合、観察は何らかのコンテキスト・チャネル照合技術を介して患者に照合される必要があり、患者に照合されれば、その時点で本要素を更新する必要がある。</t>
+    <t>原則subjectを記述すべきだが、対象患者が不明なデバイス観察のケースを考慮し、cardinalityは0..1とする。</t>
   </si>
   <si>
     <t>あなたが彼らが誰または何をしているのかわからない場合、観察には価値がありません。 / Observations have no value if you don't know who or what they're about.</t>
@@ -1144,7 +1144,7 @@
     <t>subject 要素が実際のobservationの対象でない場合に、observation の対象物。 【JP Core仕様】未使用</t>
   </si>
   <si>
-    <t>T通常、observationは対象（患者、または患者のグループ、場所、またはデバイス）について行われ、対象とobservationのために直接測定されるものとの区別は、observationコード自体（例：「血糖値」 ）で記述され、この要素を使用して個別に表す必要はない。検体（標本）への参照が必要な場合は、 `specimen`要素を使用する。リソースの代わりにコードが必要な場合は、人体部位には`bodysite`要素を使用するか、標準の拡張機能[focusCode]（extension-observation-focuscode.html）を使用する。</t>
+    <t>通常、observationは対象（患者、または患者のグループ、場所、またはデバイス）について行われ、対象とobservationのために直接測定されるものとの区別は、observationコード自体（例：「血糖値」 ）で記述され、この要素を使用して個別に表す必要はない。検体（標本）への参照が必要な場合は、 `specimen`要素を使用する。リソースの代わりにコードが必要な場合は、人体部位には`bodysite`要素を使用するか、標準の拡張機能[focusCode]（extension-observation-focuscode.html）を使用する。</t>
   </si>
   <si>
     <t>participation[typeCode=SBJ]</t>
@@ -1845,7 +1845,7 @@
     <t>複数のObservation をグループに一緒にまとめる方法については、以下の[Notes]（observation.html＃notes）を参照すること。</t>
   </si>
   <si>
-    <t>コンポーネントobservation は プライマリobservation としてのobservation リソースの中で同じ属性を共有し、常に単一のobservation の一部として扱われる（つまりそれらは分離可能ではないん）。ただし、プライマリobservationのreference rangeはコンポーネント値に継承されないため、reference rangeは各コンポーネントobservation に適切であれば必要である。</t>
+    <t>コンポーネントobservation は プライマリobservation としてのobservation リソースの中で同じ属性を共有し、常に単一のobservation の一部として扱われる（つまりそれらは分離可能ではない）。ただし、プライマリobservationのreference rangeはコンポーネント値に継承されないため、reference rangeは各コンポーネントobservation に適切であれば必要である。</t>
   </si>
   <si>
     <t>containment by OBX-4?</t>
